--- a/company_cross_reference.xlsx
+++ b/company_cross_reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thipom\Desktop\Inv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{5076D61E-430C-46D1-8345-0A26C37AF472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{577BD982-6338-4D46-B805-42B54E2D6A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4571" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4564" uniqueCount="1181">
   <si>
     <t>Company</t>
   </si>
@@ -1383,30 +1383,15 @@
     <t>ABB Inc., ABB Schweiz AG (ABB Switzerland Ltd), ABB India Limited, ABB Oy, ABB AB, ABB S.p.A., ABB Limited (UK), ABB (China) Co., Ltd., B&amp;R Industrial Automation GmbH, ABB E-mobility Holding AG</t>
   </si>
   <si>
-    <t>Dragados, S.A., HOCHTIEF Aktiengesellschaft, Iridium Concesiones de Infraestructuras, S.A.</t>
-  </si>
-  <si>
     <t>Acadia Healthcare Company, Inc.</t>
   </si>
   <si>
-    <t>Sierra Tucson, Inc., Timberline Knolls Residential Treatment Center, LLC, Oasis Behavioral Health, LLC, Rolling Hills Hospital, LLC, Red River Hospital, LLC, Peak Behavioral Health Services, LLC</t>
-  </si>
-  <si>
     <t>Accenture plc</t>
   </si>
   <si>
-    <t>Accenture LLP, Accenture Federal Services, LLC, Avanade Inc., Accenture Solutions Private Limited, Accenture (UK) Limited, Droga5, LLC, Mackevision Medien Design GmbH, Karmarama Limited, The Monkeys Pty Ltd</t>
-  </si>
-  <si>
-    <t>Syngenta Group Co., Ltd.</t>
-  </si>
-  <si>
     <t>Sinochem Holdings Corporation Ltd.</t>
   </si>
   <si>
-    <t>ADAMA Agricultural Solutions Ltd., ADAMA (Beijing) Agricultural Technology Co., Ltd.</t>
-  </si>
-  <si>
     <t>AFI Properties Ltd., Danya Cebus Ltd., Africa Israel Residences Ltd., AFI Development PLC</t>
   </si>
   <si>
@@ -1431,21 +1416,6 @@
     <t>AHAVA North America LLC, Ahava UK Ltd</t>
   </si>
   <si>
-    <t>ABX Air, Inc., Air Transport International, Inc., Omni Air International, LLC, Cargo Aircraft Management, Inc., Airborne Maintenance &amp; Engineering Services, Inc., Airborne Global Solutions, Inc., LGSTX Services, Inc.</t>
-  </si>
-  <si>
-    <t>Airbnb Ireland UC, Airbnb Payments, Inc., Hotel Tonight, Inc., Luxury Retreats International Inc., Airbnb Internet (Beijing) Co., Ltd., Airbnb Singapore Private Limited</t>
-  </si>
-  <si>
-    <t>Airbus S.A.S., Airbus Helicopters SAS, Airbus Defence and Space GmbH, Airbus Defence and Space SAS, Airbus Defence and Space Ltd, Airbus Defence and Space S.A.U., Airbus Protect SAS, Airbus UpNext SAS, Metron Aviation, Inc., Airbus Transport International SAS, Airbus Americas, Inc., Airbus China Limited</t>
-  </si>
-  <si>
-    <t>Allison Transmission, Inc., Allison Transmission Netherlands B.V., Allison Transmission India Private Limited, Vantage Power Limited, Walker Die Casting, Inc., C&amp;R Tool and Engineering, Inc.</t>
-  </si>
-  <si>
-    <t>Blue Square Real Estate Ltd. (BSRE), Mega Retail Ltd. (Mega, Mega Baâ€™Ir), Dor Alon Energy in Israel (1988) Ltd., Naaman Group (1987) Ltd.</t>
-  </si>
-  <si>
     <t>Amot Investments Ltd., Carr Properties, Brockton Everlast</t>
   </si>
   <si>
@@ -1461,54 +1431,27 @@
     <t>Amazon.com, Inc.</t>
   </si>
   <si>
-    <t>Amazon Web Services, Inc., Whole Foods Market, Inc., Twitch Interactive, Inc., Audible, Inc., Ring LLC, Zoox, Inc., Zappos.com, LLC, AbeBooks Inc., Goodreads, Inc., Metro-Goldwyn-Mayer Studios Inc., Amazon MGM Studios Distribution LLC, IMDb.com, Inc., Kuiper Systems LLC, Amazon Robotics LLC, PillPack, LLC, Woot, Inc., Amazon.com Services LLC, Amazon Payments, Inc.</t>
-  </si>
-  <si>
     <t>KPS Capital Partners, LP</t>
   </si>
   <si>
-    <t>General Engine Products, LLC (GEP), Mobility Ventures LLC, General Transmission Products, LLC (GTP)</t>
-  </si>
-  <si>
-    <t>Amir Agricultural Centers (Retail Division), Agri-Inputs Distribution Division (B2B)</t>
-  </si>
-  <si>
-    <t>Tnufa Transportation Solutions Ltd., School and Institutional Transportation Division</t>
-  </si>
-  <si>
     <t>Alony Hetz Properties and Investments Ltd.</t>
   </si>
   <si>
-    <t>Amot Energy Ltd., Offices and High-Tech Properties Division, Logistics and Industrial Properties Division</t>
-  </si>
-  <si>
     <t>Amphenol Corporation</t>
   </si>
   <si>
     <t>Amphenol Communications Solutions (ACS), Amphenol Aerospace Operations (AAO), Amphenol RF, Times Microwave Systems, SV Microwave, Amphenol Advanced Sensors, Amphenol Fiber Systems International (AFSI), Amphenol Procom, Positronic, Amphenol PCD, Amphenol Sine Systems, Amphenol LTW, Amphenol Industrial Products Group (AIPG), Amphenol Network Solutions, Amphenol Air LB, Amphenol NEXUS Technologies, Amphenol Printed Circuits</t>
   </si>
   <si>
-    <t>Residential &amp; Small Business LPG Division, Industrial &amp; Commercial LPG Division, Engineering, Installation &amp; Maintenance Division</t>
-  </si>
-  <si>
     <t>OnAccess, OnWatch, Insight</t>
   </si>
   <si>
     <t>Apollo Global Management, Inc.</t>
   </si>
   <si>
-    <t>Apollo Asset Management, Inc., Athene Holding Ltd.</t>
-  </si>
-  <si>
-    <t>Aramark Services, Inc., Avendra, LLC, Aramark Canada Ltd., Aramark Limited</t>
-  </si>
-  <si>
     <t>Archer-Daniels-Midland Company</t>
   </si>
   <si>
-    <t>ADM Investor Services, Inc., ADM International, WILD Flavors GmbH, Golden Peanut Company,  American River Transportation Company (ARTCO), ADM Milling Company, ADM Agri-Industries Company, Specialty Commodities, Inc., Probiotics International Ltd (Protexin), ADM do Brasil Ltda.</t>
-  </si>
-  <si>
     <t>Hayotzer Winery, Arza Grape Juice &amp; Sacramental Wines</t>
   </si>
   <si>
@@ -1542,18 +1485,12 @@
     <t>KKR &amp; Co. Inc.</t>
   </si>
   <si>
-    <t>Axon Enterprise, Inc.</t>
-  </si>
-  <si>
     <t>Bezeq The Israel Telecommunication Corp. Ltd., B Communications (SP1) Ltd.</t>
   </si>
   <si>
     <t>Gaon Agro Industries Ltd., Gadot Biochemical Industries Ltd.</t>
   </si>
   <si>
-    <t>BAE Systems (Holdings) Limited, BAE Systems, Inc., BAE Systems Australia Limited, BAE Systems Hägglunds AB, BAE Systems Bofors AB</t>
-  </si>
-  <si>
     <t>Leumi Partners Ltd., Bank Leumi (UK) plc, Leumi Capital Market Services Ltd.</t>
   </si>
   <si>
@@ -1563,9 +1500,6 @@
     <t>F.I.B.I. Holdings Ltd.</t>
   </si>
   <si>
-    <t>Bank Massad Ltd., Retail Banking Division</t>
-  </si>
-  <si>
     <t>Baran Engineering and Projects Ltd., Baran International Ltd.</t>
   </si>
   <si>
@@ -1581,15 +1515,9 @@
     <t>Pelephone Communications Ltd., Bezeq International Ltd., DBS Satellite Services (1998) Ltd., Bezeq OnLine Ltd., B144 Ltd.</t>
   </si>
   <si>
-    <t>Hana Liqueurs, Binyamina Winery Visitor Center &amp; Hospitality</t>
-  </si>
-  <si>
     <t>Israel Aerospace Industries (IAI)</t>
   </si>
   <si>
-    <t>Cyient Solutions &amp; Systems Private Limited (CSS), Unmanned Aerial Systems (UAS) Platforms Division</t>
-  </si>
-  <si>
     <t>Boeing Capital Corporation, Jeppesen Sanderson, ForeFlight LLC, Insitu, Aurora Flight Sciences Corporation, Millennium Space Systems LLC, Spectrolab Inc., Tapestry Solutions Inc., Argon ST Inc., Boeing Distribution Inc.</t>
   </si>
   <si>
@@ -1617,9 +1545,6 @@
     <t>Shanghai State-owned Assets Supervision and Administration Commission (Shanghai SASAC)</t>
   </si>
   <si>
-    <t>Bright Dairy Holdings (Synlait) Limited, Shanghai Bright Dairy &amp; Food Sales Co., Ltd.</t>
-  </si>
-  <si>
     <t>BRP Inc.</t>
   </si>
   <si>
@@ -1671,9 +1596,6 @@
     <t>Carlyle Investment Management LLC, AlpInvest Partners B.V., Metropolitan Real Estate Equity Management LLC, Carlyle Group Management LLC</t>
   </si>
   <si>
-    <t>Carrefour Hypermarches SAS, CSF SAS (Carrefour Supermarches France), Carrefour Proximite France SAS, Carrefour Supply Chain SAS, Carrefour Banque S.A., Carrefour Property France SAS, Atacadao S.A. (Grupo Carrefour Brasil), Centros Comerciales Carrefour, S.A., Carrefour Italia S.r.l., Carrefour Belgium SA, Carrefour Polska Sp. z o.o., Carrefour Romania S.A., Carrefour Argentina S.A., Carrefour Taiwan Co. Ltd.</t>
-  </si>
-  <si>
     <t>Hoodies Ltd., Castro</t>
   </si>
   <si>
@@ -1695,9 +1617,6 @@
     <t>Cemtrex Inc.</t>
   </si>
   <si>
-    <t>Vicon Industries Inc., Cemtrex Technologies Private Limited, Cemtrex XR (formerly Cemtrex Labs)</t>
-  </si>
-  <si>
     <t>Chevron Corporation</t>
   </si>
   <si>
@@ -1716,9 +1635,6 @@
     <t>Chocoladefabriken Lindt &amp; Sprungli AG</t>
   </si>
   <si>
-    <t>Lindt &amp; Sprungli (Schweiz) AG, Lindt &amp; Sprungli (USA) Inc., Caffarel S.p.A., Lindt &amp; Sprungli (International) AG</t>
-  </si>
-  <si>
     <t>Cisco Systems Inc.</t>
   </si>
   <si>
@@ -1734,9 +1650,6 @@
     <t>Access Industries</t>
   </si>
   <si>
-    <t>Mashav - Initiation and Development Ltd., Clal Biotechnology Industries Ltd. (TASE: CBI)</t>
-  </si>
-  <si>
     <t>Clal Insurance Company Ltd., Clal Pension and Provident Ltd.</t>
   </si>
   <si>
@@ -1746,9 +1659,6 @@
     <t>The Coca-Cola Company</t>
   </si>
   <si>
-    <t>Coca-Cola Beverages Africa (Pty) Ltd, Coca-Cola Beverages South Africa (Pty) Ltd, Coca-Cola Beverages Kenya Ltd, Coca-Cola Beverages Uganda Ltd, Coca-Cola Beverages Tanzania Ltd, Coca-Cola Beverages Mozambique SA, Coca-Cola Beverages Zambia Ltd, Costa Limited, Costa Express Limited, The Minute Maid Company, fairlife LLC, BA Sports Nutrition LLC, Energy Brands Inc., innocent Limited, Coca-Cola Refreshments USA Inc., Coca-Cola India Private Limited, Coca-Cola Ltd. (Canada), Coca-Cola (Japan) Company, CHI Limited, Coca-Cola Far East Limited, The Coca-Cola Export Corporation, Coca-Cola Services N.V./S.A.</t>
-  </si>
-  <si>
     <t>Hyundai Motor Israel, Mercedes Benz Israel, Mitsubishi Motors Israel, Mitsubishi FUSO Israel, Colmobil Next</t>
   </si>
   <si>
@@ -1767,9 +1677,6 @@
     <t>Costco Wholesale Corporation</t>
   </si>
   <si>
-    <t>Costco Wholesale Canada Ltd., Costco de Mexico S.A. de C.V., Costco Wholesale Japan Ltd., Costco Korea Ltd., Costco Wholesale UK Limited, Costco Wholesale Australia Pty Ltd, Costco Wholesale Spain S.L.U., Costco France SAS, Costco Wholesale New Zealand Limited, Costco President Taiwan Inc., Costco Logistics, Costco Travel, Costco (Shanghai) Trading Co. Ltd., Lincoln Premium Poultry LLC</t>
-  </si>
-  <si>
     <t>Covenant Aviation Security LLC, Covenant Security Services Ltd.</t>
   </si>
   <si>
@@ -2067,18 +1974,9 @@
     <t>Harel Insurance Company Ltd., Harel Pension and Provident Ltd., Harel Finance Ltd., Shomera Insurance Company Ltd.</t>
   </si>
   <si>
-    <t>Italcementi S.p.A., Lehigh Hanson, Inc. (operating as Heidelberg Materials North America), Hanson UK, PT Indocement Tunggal Prakarsa Tbk, Cementa AB, HC Trading GmbH, HeidelbergCement India Limited, Hanson Australia Pty Ltd, Devnya Cement AD</t>
-  </si>
-  <si>
     <t>Printing and Personal Systems (PPS), Enterprise Group, HP Enterprise Services, HP Software, HP Financial Services Company, Hewlett-Packard Development Company, L.P.</t>
   </si>
   <si>
-    <t>HIDROMEK West, OOO HIDROMEK RUS, HIDROMEK Thailand</t>
-  </si>
-  <si>
-    <t>Ness Technologies (Israel) Ltd., Hilan HR &amp; Payroll Solutions Division</t>
-  </si>
-  <si>
     <t>The Hongkong and Shanghai Banking Corporation Limited, HSBC Bank plc, HSBC UK Holdings Limited, HSBC North America Holdings Inc.</t>
   </si>
   <si>
@@ -2148,9 +2046,6 @@
     <t>TSG IT Advanced Systems Ltd. (Ness TSG), NessPRO Marketing of Computer Systems Ltd. (NessPRO)</t>
   </si>
   <si>
-    <t>Northrop Grumman Systems Corporation, SpaceLogistics LLC, Northrop Grumman UK Limited, Northrop Grumman Australia Pty Ltd</t>
-  </si>
-  <si>
     <t>Nuctech Netherlands B.V., Nuctech Warsaw Company Limited sp. z o.o.</t>
   </si>
   <si>
@@ -2184,9 +2079,6 @@
     <t>Cofix Group Ltd., Rami Levy Hashikma Marketing Communications Ltd.</t>
   </si>
   <si>
-    <t>Rapiscan Systems Limited, Rapiscan Systems (M) Sdn. Bhd.</t>
-  </si>
-  <si>
     <t>Regions Bank, Regions Securities LLC</t>
   </si>
   <si>
@@ -2196,9 +2088,6 @@
     <t>Manna Irrigation Ltd., Eurodrip S.A.</t>
   </si>
   <si>
-    <t>Rolls-Royce plc, Rolls-Royce Power Systems AG, Rolls-Royce SMR Limited</t>
-  </si>
-  <si>
     <t>Rothstein Urban Renewal Ltd., Rothstein Initiation &amp; Construction Ltd.</t>
   </si>
   <si>
@@ -2217,9 +2106,6 @@
     <t>Shapir Civil and Marine Engineering Ltd., Shapir Industrial Plants Ltd.</t>
   </si>
   <si>
-    <t>New-Pharm Drugstores Ltd. (BE by Shufersal), Shufersal Finance (2006) Ltd.</t>
-  </si>
-  <si>
     <t>SMARTSHOOTER Inc., SMARTSHOOTER UK Ltd.</t>
   </si>
   <si>
@@ -2229,9 +2115,6 @@
     <t>Pine Tree Castings, Marlin Firearms</t>
   </si>
   <si>
-    <t>D. Swarovski KG, Swarovski Aktiengesellschaft (Swarovski AG), Swarovski Crystal Online AG, Swarovski Optik KG, Tyrolit Schleifmittelwerke Swarovski K.G., Swarovski North America Limited, Swarovski (UK) Limited, Swarovski India Private Limited</t>
-  </si>
-  <si>
     <t>TAHAL Consulting Engineers Ltd., TAHAL Consulting Engineers India Private Limited</t>
   </si>
   <si>
@@ -2313,9 +2196,6 @@
     <t>Hebei Jing'ao Solar Energy Co. Ltd., JA Solar USA Inc., JA Solar GmbH, JA Solar Japan Co. Ltd., JA Solar Singapore Pte. Ltd., JA Solar Malaysia Sdn. Bhd., JA Solar Vietnam Company Limited, JA Solar International Limited</t>
   </si>
   <si>
-    <t>Jaguar Land Rover Holdings Limited, Jaguar Land Rover Limited, Jaguar Land Rover International Limited, Jaguar Land Rover North America, LLC, Jaguar Land Rover (China) Investment Co., Ltd., Jaguar Land Rover India Limited, Jaguar Land Rover Slovakia s.r.o., Jaguar Land Rover Deutschland GmbH, Jaguar Land Rover Australia Pty Ltd, Jaguar Land Rover Canada ULC, Jaguar Land Rover Espana, S.L., Jaguar Land Rover Italia S.p.A., InMotion Ventures Ltd</t>
-  </si>
-  <si>
     <t>J.C. Bamford Excavators Limited, JCB Sales Limited, JCB Service, JCB Finance Limited, JCB Power Systems Limited, JCB Heavy Products Limited, JCB Earthmovers Limited, JCB Compact Products Limited, JCB Cab Systems Limited, JCB India Limited, JCB Inc. (JCB North America), JCB Brasil Equipamentos Ltda, JCB (China) Investment Co. Ltd., JCB Deutschland GmbH, JCB Middle East FZCO, JCB Maquinaria S.A.</t>
   </si>
   <si>
@@ -2337,9 +2217,6 @@
     <t>Manitou Americas Inc., Manitou UK Ltd, Manitou Australia Pty Ltd, Manitou Benelux NV/SA, Manitou Deutschland GmbH, Manitou Asia Pte Ltd, Manitou South Africa (Pty) Ltd, Manitou Equipment India Private Limited</t>
   </si>
   <si>
-    <t>McDonald's USA LLC, McDonald's Restaurants Limited, McDonald's Restaurants of Canada Limited, McDonald's Australia Limited, McD Global Franchising Ltd., McDonald's Real Estate Company, McDonald's Deutschland LLC, McDonald's France SAS</t>
-  </si>
-  <si>
     <t>Mekorot Development &amp; Enterprise Ltd., WaTech Mekorot Water Technology Innovation Center</t>
   </si>
   <si>
@@ -2352,9 +2229,6 @@
     <t>LinkedIn Corporation, GitHub Inc., Mojang AB (Mojang Studios), ZeniMax Media Inc., Activision Blizzard Inc., Skype Communications, Microsoft Ireland Operations Limited</t>
   </si>
   <si>
-    <t>Airwave Solutions Limited, Avigilon Corporation, VaaS International Holdings Inc., WatchGuard Inc. (WatchGuard Video), Spillman Technologies Inc., Openpath Security Inc., Ava Security Ltd., Calipsa Ltd., Envysion Inc., TRX Systems Inc., Callyo 2009 Corp., Futurecom Systems Group, ULC, Edesix Limited, Kodiak Networks Inc., Rave Mobile Safety (Rave Wireless Inc.)</t>
-  </si>
-  <si>
     <t>NaanDanJain Iberica S.L., NaanDanJain Mexico S.A. de C.V.</t>
   </si>
   <si>
@@ -2364,9 +2238,6 @@
     <t>Orbia Advance Corporation S.A.B. de C.V.</t>
   </si>
   <si>
-    <t>Netafim USA (Netafim Irrigation Inc.), Netafim India Private Limited, Netafim Brazil, Netafim Mexico, Netafim China, Netafim South Africa (Pty) Ltd, Netafim Australia Pty Ltd, Netafim Italy, Netafim France, Netafim Iberia (Spain/Portugal), Netafim Turkey, Netafim Chile</t>
-  </si>
-  <si>
     <t>NICE CXone Inc., NICE Actimize Inc., LiveVox Holdings Inc., Nexidia Inc., Mattersight Corporation, Teleopti AB, NICE Systems Inc., NICE Systems UK Limited</t>
   </si>
   <si>
@@ -2385,9 +2256,6 @@
     <t>JLG Industries Inc., Oshkosh Defense LLC, Pierce Manufacturing Inc., Oshkosh Airport Products LLC, McNeilus Truck and Manufacturing Inc., Iowa Mold Tooling Co. Inc. (IMT), Oshkosh AeroTech LLC</t>
   </si>
   <si>
-    <t>Palantir USG Inc., Palantir Technologies UK Ltd, Palantir Technologies Japan K.K., Palantir Technologies Australia Pty Ltd, Palantir Technologies GmbH, Palantir Technologies Singapore Pte. Ltd.</t>
-  </si>
-  <si>
     <t>PA Consulting Services Limited, PA Consulting Group Inc., PA Consulting Group AB, PA Consulting Group A/S, PA Consulting Group AS, Sparkler Limited, We Are Friday Limited, Essential Design Inc., Astro Studios Inc., Nyras Limited</t>
   </si>
   <si>
@@ -2400,9 +2268,6 @@
     <t>DS Services of America Inc., Glacier Water Services Inc., Aquaterra Corporation</t>
   </si>
   <si>
-    <t>Psagot Winery Visitor Center &amp; Events</t>
-  </si>
-  <si>
     <t>RMCO LLC, Real Estate Segment (RE/MAX), Motto Mortgage, wemlo</t>
   </si>
   <si>
@@ -2433,9 +2298,6 @@
     <t>SolarEdge Technologies Inc.</t>
   </si>
   <si>
-    <t>SolarEdge Technologies Ltd., SolarEdge Technologies GmbH, SolarEdge Technologies (Australia) Pty Ltd, SolarEdge Technologies Japan K.K., SolarEdge Technologies UK Ltd, Kokam Co. Ltd., Hark Systems Ltd.</t>
-  </si>
-  <si>
     <t xml:space="preserve">SuperPharm Limited </t>
   </si>
   <si>
@@ -2445,18 +2307,6 @@
     <t>Shipt Inc., Target Brands Inc., Target Enterprise Inc.</t>
   </si>
   <si>
-    <t>Efrat Winery, Teperberg 1870 Visitor Center</t>
-  </si>
-  <si>
-    <t>Teva Pharmaceuticals USA Inc., Cephalon Inc., Teva Pharmaceuticals Europe B.V., Teva UK Limited, Teva Canada Limited, PLIVA Hrvatska d.o.o. (PLIVA Croatia), ratiopharm GmbH, Teva Pharmaceuticals International GmbH, TEVA Czech Industries s.r.o.</t>
-  </si>
-  <si>
-    <t>Thales Alenia Space S.A.S., Thales DIS France SAS, Thales UK Limited, Thales Australia Limited, Thales Nederland B.V., Thales Deutschland GmbH, Thales Canada Inc., Thales USA Inc., Thales Defense &amp; Security Inc., Omnisys Engenharia S.A., Thales Solutions Asia Pte. Ltd., Thales AVS France SAS</t>
-  </si>
-  <si>
-    <t>Fisher Scientific Company L.L.C., Life Technologies Corporation, PPD Inc., Patheon Inc., FEI Company, Dionex Corporation, Affymetrix Inc., Phadia AB, Mesa Biotech Inc., The Binding Site Group Ltd, Remel Inc., One Lambda Inc., Pierce Biotechnology Inc.</t>
-  </si>
-  <si>
     <t>Track Group Chile SpA</t>
   </si>
   <si>
@@ -3261,9 +3111,6 @@
     <t>Maersk A/S, APM Terminals B.V., Hamburg Sudamerikanische Dampfschifffahrts-Gesellschaft A/S &amp; Co. KG, Maersk Air Cargo A/S, Maersk Logistics &amp; Services International A/S, Maersk Oil Trading and Investments A/S, Maersk Training A/S</t>
   </si>
   <si>
-    <t>telerob Gesellschaft fur Fernhantierungstechnik mbH, Arcturus UAV, Inc., Tomahawk Robotics, LLC</t>
-  </si>
-  <si>
     <t>Alphabet Inc.</t>
   </si>
   <si>
@@ -3588,9 +3435,6 @@
     <t>Insider Inc., Politico LLC, The Stepstone Group SE, AVIV Group, Axel Springer Deutschland GmbH, idealo internet GmbH, Bonial International GmbH, upday GmbH &amp; Co. KG, finanzen.net GmbH</t>
   </si>
   <si>
-    <t>Axon Federal, Inc., Fusus Inc., Sky-Hero SA/NV, Axon Public Safety UK Ltd</t>
-  </si>
-  <si>
     <t>Isracard Ltd., Hapoalim Securities USA, Inc.</t>
   </si>
   <si>
@@ -3601,6 +3445,141 @@
   </si>
   <si>
     <t>AFSC Divesment List 2025, WhoProfits List</t>
+  </si>
+  <si>
+    <t>Syngenta Group Co. Ltd.</t>
+  </si>
+  <si>
+    <t>ADAMA Agricultural Solutions Ltd., ADAMA (Beijing) Agricultural Technology Co. Ltd.</t>
+  </si>
+  <si>
+    <t>ABX Air Inc., Air Transport International Inc., Omni Air International LLC, Cargo Aircraft Management Inc., Airborne Maintenance &amp; Engineering Services Inc., Airborne Global Solutions Inc., LGSTX Services Inc.</t>
+  </si>
+  <si>
+    <t>Airbnb Ireland UC, Airbnb Payments Inc., Hotel Tonight Inc., Luxury Retreats International Inc., Airbnb Internet (Beijing) Co. Ltd., Airbnb Singapore Private Limited</t>
+  </si>
+  <si>
+    <t>Airbus S.A.S., Airbus Helicopters SAS, Airbus Defence and Space GmbH, Airbus Defence and Space SAS, Airbus Defence and Space Ltd, Airbus Defence and Space S.A.U., Airbus Protect SAS, Airbus UpNext SAS, Metron Aviation Inc., Airbus Transport International SAS, Airbus Americas Inc., Airbus China Limited</t>
+  </si>
+  <si>
+    <t>Sierra Tucson Inc., Timberline Knolls Residential Treatment Center LLC, Oasis Behavioral Health LLC, Rolling Hills Hospital LLC, Red River Hospital LLC, Peak Behavioral Health Services LLC</t>
+  </si>
+  <si>
+    <t>Accenture LLP, Accenture Federal Services LLC, Avanade Inc., Accenture Solutions Private Limited, Accenture (UK) Limited, Droga5 LLC, Mackevision Medien Design GmbH, Karmarama Limited, The Monkeys Pty Ltd</t>
+  </si>
+  <si>
+    <t>Dragados S.A., HOCHTIEF Aktiengesellschaft, Iridium Concesiones de Infraestructuras S.A.</t>
+  </si>
+  <si>
+    <t>telerob Gesellschaft fur Fernhantierungstechnik mbH, Arcturus UAV Inc., Tomahawk Robotics LLC</t>
+  </si>
+  <si>
+    <t>Allison Transmission Inc., Allison Transmission Netherlands B.V., Allison Transmission India Private Limited, Vantage Power Limited, Walker Die Casting, Inc., C&amp;R Tool and Engineering Inc.</t>
+  </si>
+  <si>
+    <t>Blue Square Real Estate Ltd. (BSRE), Mega Retail Ltd., Dor Alon Energy in Israel (1988) Ltd., Naaman Group (1987) Ltd.</t>
+  </si>
+  <si>
+    <t>General Engine Products LLC (GEP), Mobility Ventures LLC, General Transmission Products LLC</t>
+  </si>
+  <si>
+    <t>Amazon Web Services Inc., Whole Foods Market Inc., Twitch Interactive Inc., Audible Inc., Ring LLC, Zoox Inc., Zappos.com LLC, AbeBooks Inc., Goodreads Inc., Metro-Goldwyn-Mayer Studios Inc., Amazon MGM Studios Distribution LLC, IMDb.com Inc., Kuiper Systems LLC, Amazon Robotics LLC, PillPack LLC, Woot Inc., Amazon.com Services LLC, Amazon Payments, Inc.</t>
+  </si>
+  <si>
+    <t>Tnufa Transportation Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>Amot Energy Ltd.</t>
+  </si>
+  <si>
+    <t>Apollo Asset Management Inc., Athene Holding Ltd.</t>
+  </si>
+  <si>
+    <t>Aramark Services, Inc., Avendra LLC, Aramark Canada Ltd., Aramark Limited</t>
+  </si>
+  <si>
+    <t>ADM Investor Services Inc., ADM International, WILD Flavors GmbH, Golden Peanut Company,  American River Transportation Company (ARTCO), ADM Milling Company, ADM Agri-Industries Company, Specialty Commodities Inc., Probiotics International Ltd (Protexin), ADM do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>Axon Federal Inc., Fusus Inc., Sky-Hero SA/NV, Axon Public Safety UK Ltd</t>
+  </si>
+  <si>
+    <t>Axon Enterprise Inc.</t>
+  </si>
+  <si>
+    <t>BAE Systems (Holdings) Limited, BAE Systems Inc., BAE Systems Australia Limited, BAE Systems Hägglunds AB, BAE Systems Bofors AB</t>
+  </si>
+  <si>
+    <t>Bank Massad Ltd.</t>
+  </si>
+  <si>
+    <t>Hana Liqueurs,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyient Solutions &amp; Systems Private Limited </t>
+  </si>
+  <si>
+    <t>Bright Dairy Holdings (Synlait) Limited, Shanghai Bright Dairy &amp; Food Sales Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Carrefour Hypermarches SAS, CSF SAS (Carrefour Supermarches France)</t>
+  </si>
+  <si>
+    <t>Vicon Industries Inc., Cemtrex Technologies Private Limited, Cemtrex XR</t>
+  </si>
+  <si>
+    <t>Caffarel S.p.A., Lindt &amp; Sprungli</t>
+  </si>
+  <si>
+    <t>Mashav - Initiation and Development Ltd., Clal Biotechnology Industries Ltd.</t>
+  </si>
+  <si>
+    <t>Costa Limited, Costa Express Limited, The Minute Maid Company, fairlife LLC, BA Sports Nutrition LLC, Energy Brands Inc., innocent Limited, CHI Limited</t>
+  </si>
+  <si>
+    <t>Lincoln Premium Poultry LLC</t>
+  </si>
+  <si>
+    <t>Italcementi S.p.A., Lehigh Hanson Inc., Heidelberg Materials North America, Hanson UK, PT Indocement Tunggal Prakarsa Tbk, Cementa AB, HC Trading GmbH, Heidelberg Cement India Limited, Hanson Australia Pty Ltd, Devnya Cement AD</t>
+  </si>
+  <si>
+    <t>Ness Technologies Ltd., Hilan HR &amp; Payroll Solutions</t>
+  </si>
+  <si>
+    <t>InMotion Ventures Ltd</t>
+  </si>
+  <si>
+    <t>McDonald's USA LLC, McDonald's Restaurants Limited, McD Global Franchising Ltd., McDonald's Real Estate Company</t>
+  </si>
+  <si>
+    <t>Airwave Solutions Limited, Avigilon Corporation, VaaS International Holdings Inc., WatchGuard Inc. (WatchGuard Video), Spillman Technologies Inc., Openpath Security Inc., Ava Security Ltd., Calipsa Ltd., Envysion Inc., TRX Systems Inc., Callyo 2009 Corp., Futurecom Systems Group, ULC, Edesix Limited, Kodiak Networks Inc., Rave Mobile Safety, Rave Wireless Inc.</t>
+  </si>
+  <si>
+    <t>Northrop Grumman Systems Corporation, SpaceLogistics LLC</t>
+  </si>
+  <si>
+    <t>Rolls-Royce plc, Rolls-Royce Power Systems AG</t>
+  </si>
+  <si>
+    <t>New-Pharm Drugstores Ltd., BE by Shufersal, Shufersal Finance (2006) Ltd.</t>
+  </si>
+  <si>
+    <t>Kokam Co. Ltd., Hark Systems Ltd.</t>
+  </si>
+  <si>
+    <t>D. Swarovski KG, Swarovski Aktiengesellschaft (Swarovski AG), Swarovski Crystal Online AG, Swarovski Optik KG, Tyrolit Schleifmittelwerke Swarovski K.G.</t>
+  </si>
+  <si>
+    <t>Efrat Winery</t>
+  </si>
+  <si>
+    <t>Cephalon Inc., PLIVA Hrvatska d.o.o. (PLIVA Croatia), ratiopharm GmbH</t>
+  </si>
+  <si>
+    <t>Thales Alenia Space S.A.S., Thales Defense &amp; Security Inc., Omnisys Engenharia S.A.</t>
+  </si>
+  <si>
+    <t>Fisher Scientific Company LLC, Life Technologies Corporation, PPD Inc., Patheon Inc., FEI Company, Dionex Corporation, Affymetrix Inc., Phadia AB, Mesa Biotech Inc., The Binding Site Group Ltd, Remel Inc., One Lambda Inc., Pierce Biotechnology Inc.</t>
   </si>
 </sst>
 </file>
@@ -4469,7 +4448,7 @@
         <v>430</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4501,7 +4480,7 @@
         <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -4529,7 +4508,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>856</v>
+        <v>806</v>
       </c>
       <c r="E4" t="s">
         <v>4</v>
@@ -4609,16 +4588,16 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>857</v>
+        <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>1071</v>
+        <v>1021</v>
       </c>
       <c r="C8" t="s">
-        <v>1072</v>
+        <v>1022</v>
       </c>
       <c r="D8" t="s">
-        <v>1073</v>
+        <v>1023</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
@@ -4633,7 +4612,7 @@
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -4679,7 +4658,7 @@
         <v>5</v>
       </c>
       <c r="I10" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4687,10 +4666,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D11" t="s">
-        <v>450</v>
+        <v>1141</v>
       </c>
       <c r="E11" t="s">
         <v>4</v>
@@ -4705,7 +4684,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -4713,10 +4692,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D12" t="s">
-        <v>452</v>
+        <v>1142</v>
       </c>
       <c r="E12" t="s">
         <v>4</v>
@@ -4731,7 +4710,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -4782,7 +4761,7 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>448</v>
+        <v>1143</v>
       </c>
       <c r="E15" t="s">
         <v>4</v>
@@ -4825,13 +4804,13 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>453</v>
+        <v>1136</v>
       </c>
       <c r="C17" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D17" t="s">
-        <v>455</v>
+        <v>1137</v>
       </c>
       <c r="E17" t="s">
         <v>4</v>
@@ -4846,7 +4825,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -4871,10 +4850,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>888</v>
+        <v>838</v>
       </c>
       <c r="D19" t="s">
-        <v>1124</v>
+        <v>1073</v>
       </c>
       <c r="E19" t="s">
         <v>4</v>
@@ -4894,10 +4873,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>858</v>
+        <v>808</v>
       </c>
       <c r="D20" t="s">
-        <v>1074</v>
+        <v>1144</v>
       </c>
       <c r="E20" t="s">
         <v>4</v>
@@ -4912,7 +4891,7 @@
         <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -4920,13 +4899,13 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C21" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D21" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E21" t="s">
         <v>4</v>
@@ -4941,7 +4920,7 @@
         <v>5</v>
       </c>
       <c r="I21" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -4949,13 +4928,13 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C22" t="s">
         <v>223</v>
       </c>
       <c r="D22" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E22" t="s">
         <v>4</v>
@@ -4975,7 +4954,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>889</v>
+        <v>839</v>
       </c>
       <c r="E23" t="s">
         <v>4</v>
@@ -5018,7 +4997,7 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E25" t="s">
         <v>4</v>
@@ -5058,7 +5037,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>890</v>
+        <v>840</v>
       </c>
       <c r="E27" t="s">
         <v>4</v>
@@ -5121,13 +5100,13 @@
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C30" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D30" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E30" t="s">
         <v>4</v>
@@ -5170,7 +5149,7 @@
         <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>464</v>
+        <v>1138</v>
       </c>
       <c r="E32" t="s">
         <v>4</v>
@@ -5185,7 +5164,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -5196,7 +5175,7 @@
         <v>30</v>
       </c>
       <c r="D33" t="s">
-        <v>465</v>
+        <v>1139</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
@@ -5211,7 +5190,7 @@
         <v>5</v>
       </c>
       <c r="I33" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -5219,7 +5198,7 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>466</v>
+        <v>1140</v>
       </c>
       <c r="E34" t="s">
         <v>4</v>
@@ -5234,12 +5213,12 @@
         <v>4</v>
       </c>
       <c r="I34" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>892</v>
+        <v>842</v>
       </c>
       <c r="E35" t="s">
         <v>4</v>
@@ -5259,10 +5238,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>893</v>
+        <v>843</v>
       </c>
       <c r="D36" t="s">
-        <v>1125</v>
+        <v>1074</v>
       </c>
       <c r="E36" t="s">
         <v>4</v>
@@ -5305,7 +5284,7 @@
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>467</v>
+        <v>1145</v>
       </c>
       <c r="E38" t="s">
         <v>4</v>
@@ -5320,7 +5299,7 @@
         <v>4</v>
       </c>
       <c r="I38" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -5348,7 +5327,7 @@
         <v>35</v>
       </c>
       <c r="D40" t="s">
-        <v>468</v>
+        <v>1146</v>
       </c>
       <c r="E40" t="s">
         <v>5</v>
@@ -5371,7 +5350,7 @@
         <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="E41" t="s">
         <v>4</v>
@@ -5386,18 +5365,18 @@
         <v>4</v>
       </c>
       <c r="I41" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>860</v>
+        <v>810</v>
       </c>
       <c r="C42" t="s">
-        <v>1075</v>
+        <v>1024</v>
       </c>
       <c r="D42" t="s">
-        <v>1076</v>
+        <v>1025</v>
       </c>
       <c r="E42" t="s">
         <v>4</v>
@@ -5412,7 +5391,7 @@
         <v>4</v>
       </c>
       <c r="I42" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -5420,7 +5399,7 @@
         <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="E43" t="s">
         <v>5</v>
@@ -5435,7 +5414,7 @@
         <v>4</v>
       </c>
       <c r="I43" t="s">
-        <v>1185</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -5443,10 +5422,10 @@
         <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="D44" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="E44" t="s">
         <v>5</v>
@@ -5461,12 +5440,12 @@
         <v>5</v>
       </c>
       <c r="I44" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>895</v>
+        <v>845</v>
       </c>
       <c r="E45" t="s">
         <v>4</v>
@@ -5489,10 +5468,10 @@
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="D46" t="s">
-        <v>476</v>
+        <v>1147</v>
       </c>
       <c r="E46" t="s">
         <v>4</v>
@@ -5512,7 +5491,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>861</v>
+        <v>811</v>
       </c>
       <c r="E47" t="s">
         <v>4</v>
@@ -5527,7 +5506,7 @@
         <v>4</v>
       </c>
       <c r="I47" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
@@ -5535,10 +5514,10 @@
         <v>39</v>
       </c>
       <c r="C48" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="D48" t="s">
-        <v>474</v>
+        <v>1148</v>
       </c>
       <c r="E48" t="s">
         <v>4</v>
@@ -5553,16 +5532,13 @@
         <v>4</v>
       </c>
       <c r="I48" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>41</v>
       </c>
-      <c r="D49" t="s">
-        <v>477</v>
-      </c>
       <c r="E49" t="s">
         <v>5</v>
       </c>
@@ -5576,16 +5552,13 @@
         <v>5</v>
       </c>
       <c r="I49" t="s">
-        <v>1186</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>46</v>
       </c>
-      <c r="D50" t="s">
-        <v>483</v>
-      </c>
       <c r="E50" t="s">
         <v>5</v>
       </c>
@@ -5607,7 +5580,7 @@
         <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>478</v>
+        <v>1149</v>
       </c>
       <c r="E51" t="s">
         <v>4</v>
@@ -5650,13 +5623,13 @@
         <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="C53" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="D53" t="s">
-        <v>480</v>
+        <v>1150</v>
       </c>
       <c r="E53" t="s">
         <v>4</v>
@@ -5671,7 +5644,7 @@
         <v>4</v>
       </c>
       <c r="I53" t="s">
-        <v>862</v>
+        <v>812</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -5679,10 +5652,10 @@
         <v>45</v>
       </c>
       <c r="C54" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="D54" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="E54" t="s">
         <v>4</v>
@@ -5697,12 +5670,12 @@
         <v>4</v>
       </c>
       <c r="I54" t="s">
-        <v>622</v>
+        <v>591</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>897</v>
+        <v>847</v>
       </c>
       <c r="E55" t="s">
         <v>4</v>
@@ -5737,7 +5710,7 @@
         <v>5</v>
       </c>
       <c r="I56" t="s">
-        <v>898</v>
+        <v>848</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
@@ -5765,7 +5738,7 @@
         <v>49</v>
       </c>
       <c r="D58" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E58" t="s">
         <v>4</v>
@@ -5788,10 +5761,10 @@
         <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="D59" t="s">
-        <v>486</v>
+        <v>1151</v>
       </c>
       <c r="E59" t="s">
         <v>4</v>
@@ -5806,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="I59" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -5837,7 +5810,7 @@
         <v>52</v>
       </c>
       <c r="D61" t="s">
-        <v>487</v>
+        <v>1152</v>
       </c>
       <c r="E61" t="s">
         <v>4</v>
@@ -5852,7 +5825,7 @@
         <v>4</v>
       </c>
       <c r="I61" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
@@ -5880,10 +5853,10 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="D63" t="s">
-        <v>489</v>
+        <v>1153</v>
       </c>
       <c r="E63" t="s">
         <v>4</v>
@@ -5898,12 +5871,12 @@
         <v>4</v>
       </c>
       <c r="I63" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>829</v>
+        <v>779</v>
       </c>
       <c r="E64" t="s">
         <v>5</v>
@@ -5923,7 +5896,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>830</v>
+        <v>780</v>
       </c>
       <c r="E65" t="s">
         <v>5</v>
@@ -5943,7 +5916,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>899</v>
+        <v>849</v>
       </c>
       <c r="E66" t="s">
         <v>4</v>
@@ -5966,7 +5939,7 @@
         <v>55</v>
       </c>
       <c r="D67" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="E67" t="s">
         <v>4</v>
@@ -5986,7 +5959,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="E68" t="s">
         <v>4</v>
@@ -6006,13 +5979,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>863</v>
+        <v>813</v>
       </c>
       <c r="B69" t="s">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="C69" t="s">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="E69" t="s">
         <v>4</v>
@@ -6027,7 +6000,7 @@
         <v>4</v>
       </c>
       <c r="I69" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
@@ -6038,7 +6011,7 @@
         <v>56</v>
       </c>
       <c r="D70" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="E70" t="s">
         <v>5</v>
@@ -6067,7 +6040,7 @@
         <v>56</v>
       </c>
       <c r="D71" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="E71" t="s">
         <v>5</v>
@@ -6122,7 +6095,7 @@
         <v>56</v>
       </c>
       <c r="D73" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="E73" t="s">
         <v>4</v>
@@ -6145,7 +6118,7 @@
         <v>61</v>
       </c>
       <c r="D74" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="E74" t="s">
         <v>4</v>
@@ -6168,10 +6141,10 @@
         <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="D75" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="E75" t="s">
         <v>4</v>
@@ -6186,7 +6159,7 @@
         <v>4</v>
       </c>
       <c r="I75" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
@@ -6194,10 +6167,10 @@
         <v>62</v>
       </c>
       <c r="C76" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="D76" t="s">
-        <v>1181</v>
+        <v>1130</v>
       </c>
       <c r="E76" t="s">
         <v>4</v>
@@ -6212,7 +6185,7 @@
         <v>4</v>
       </c>
       <c r="I76" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
@@ -6240,10 +6213,10 @@
         <v>63</v>
       </c>
       <c r="C78" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="D78" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="E78" t="s">
         <v>4</v>
@@ -6258,12 +6231,12 @@
         <v>5</v>
       </c>
       <c r="I78" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>901</v>
+        <v>851</v>
       </c>
       <c r="E79" t="s">
         <v>4</v>
@@ -6303,7 +6276,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>902</v>
+        <v>852</v>
       </c>
       <c r="E81" t="s">
         <v>4</v>
@@ -6338,7 +6311,7 @@
         <v>4</v>
       </c>
       <c r="I82" t="s">
-        <v>621</v>
+        <v>590</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
@@ -6346,10 +6319,10 @@
         <v>67</v>
       </c>
       <c r="C83" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="D83" t="s">
-        <v>1182</v>
+        <v>1131</v>
       </c>
       <c r="E83" t="s">
         <v>4</v>
@@ -6372,10 +6345,10 @@
         <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>501</v>
+        <v>1155</v>
       </c>
       <c r="D84" t="s">
-        <v>1183</v>
+        <v>1154</v>
       </c>
       <c r="E84" t="s">
         <v>4</v>
@@ -6390,7 +6363,7 @@
         <v>4</v>
       </c>
       <c r="I84" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -6398,7 +6371,7 @@
         <v>69</v>
       </c>
       <c r="D85" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="E85" t="s">
         <v>4</v>
@@ -6413,7 +6386,7 @@
         <v>5</v>
       </c>
       <c r="I85" t="s">
-        <v>1187</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -6421,7 +6394,7 @@
         <v>70</v>
       </c>
       <c r="D86" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="E86" t="s">
         <v>4</v>
@@ -6436,7 +6409,7 @@
         <v>5</v>
       </c>
       <c r="I86" t="s">
-        <v>896</v>
+        <v>846</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
@@ -6481,7 +6454,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>903</v>
+        <v>853</v>
       </c>
       <c r="E89" t="s">
         <v>4</v>
@@ -6507,7 +6480,7 @@
         <v>73</v>
       </c>
       <c r="D90" t="s">
-        <v>504</v>
+        <v>1156</v>
       </c>
       <c r="E90" t="s">
         <v>4</v>
@@ -6522,7 +6495,7 @@
         <v>4</v>
       </c>
       <c r="I90" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
@@ -6530,7 +6503,7 @@
         <v>74</v>
       </c>
       <c r="C91" t="s">
-        <v>1184</v>
+        <v>1132</v>
       </c>
       <c r="E91" t="s">
         <v>5</v>
@@ -6545,7 +6518,7 @@
         <v>4</v>
       </c>
       <c r="I91" t="s">
-        <v>859</v>
+        <v>809</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
@@ -6556,7 +6529,7 @@
         <v>75</v>
       </c>
       <c r="D92" t="s">
-        <v>505</v>
+        <v>484</v>
       </c>
       <c r="E92" t="s">
         <v>5</v>
@@ -6571,7 +6544,7 @@
         <v>5</v>
       </c>
       <c r="I92" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
@@ -6591,7 +6564,7 @@
         <v>4</v>
       </c>
       <c r="I93" t="s">
-        <v>859</v>
+        <v>809</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
@@ -6599,13 +6572,13 @@
         <v>77</v>
       </c>
       <c r="B94" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="C94" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="D94" t="s">
-        <v>508</v>
+        <v>1157</v>
       </c>
       <c r="E94" t="s">
         <v>4</v>
@@ -6620,7 +6593,7 @@
         <v>5</v>
       </c>
       <c r="I94" t="s">
-        <v>898</v>
+        <v>848</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
@@ -6671,7 +6644,7 @@
         <v>80</v>
       </c>
       <c r="D97" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="E97" t="s">
         <v>4</v>
@@ -6686,7 +6659,7 @@
         <v>5</v>
       </c>
       <c r="I97" t="s">
-        <v>896</v>
+        <v>846</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
@@ -6711,7 +6684,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>904</v>
+        <v>854</v>
       </c>
       <c r="E99" t="s">
         <v>4</v>
@@ -6734,10 +6707,10 @@
         <v>82</v>
       </c>
       <c r="B100" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="C100" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="E100" t="s">
         <v>4</v>
@@ -6800,7 +6773,7 @@
         <v>84</v>
       </c>
       <c r="D103" t="s">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="E103" t="s">
         <v>4</v>
@@ -6815,7 +6788,7 @@
         <v>4</v>
       </c>
       <c r="I103" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
@@ -6866,7 +6839,7 @@
         <v>88</v>
       </c>
       <c r="D106" t="s">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="E106" t="s">
         <v>4</v>
@@ -6881,7 +6854,7 @@
         <v>4</v>
       </c>
       <c r="I106" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
@@ -6909,7 +6882,7 @@
         <v>90</v>
       </c>
       <c r="D108" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="E108" t="s">
         <v>5</v>
@@ -6924,7 +6897,7 @@
         <v>5</v>
       </c>
       <c r="I108" t="s">
-        <v>1186</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
@@ -6952,7 +6925,7 @@
         <v>92</v>
       </c>
       <c r="D110" t="s">
-        <v>514</v>
+        <v>1158</v>
       </c>
       <c r="E110" t="s">
         <v>4</v>
@@ -6972,13 +6945,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>905</v>
+        <v>855</v>
       </c>
       <c r="B111" t="s">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="C111" t="s">
-        <v>1126</v>
+        <v>1075</v>
       </c>
       <c r="E111" t="s">
         <v>4</v>
@@ -6998,7 +6971,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>906</v>
+        <v>856</v>
       </c>
       <c r="E112" t="s">
         <v>4</v>
@@ -7021,13 +6994,13 @@
         <v>93</v>
       </c>
       <c r="B113" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="C113" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="D113" t="s">
-        <v>516</v>
+        <v>1159</v>
       </c>
       <c r="E113" t="s">
         <v>4</v>
@@ -7047,7 +7020,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>907</v>
+        <v>857</v>
       </c>
       <c r="E114" t="s">
         <v>4</v>
@@ -7073,7 +7046,7 @@
         <v>94</v>
       </c>
       <c r="D115" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="E115" t="s">
         <v>4</v>
@@ -7088,7 +7061,7 @@
         <v>5</v>
       </c>
       <c r="I115" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
@@ -7096,7 +7069,7 @@
         <v>97</v>
       </c>
       <c r="D116" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="E116" t="s">
         <v>4</v>
@@ -7142,7 +7115,7 @@
         <v>96</v>
       </c>
       <c r="D118" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="E118" t="s">
         <v>5</v>
@@ -7157,7 +7130,7 @@
         <v>5</v>
       </c>
       <c r="I118" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
@@ -7165,7 +7138,7 @@
         <v>98</v>
       </c>
       <c r="D119" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="E119" t="s">
         <v>4</v>
@@ -7180,7 +7153,7 @@
         <v>4</v>
       </c>
       <c r="I119" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
@@ -7208,13 +7181,13 @@
         <v>100</v>
       </c>
       <c r="B121" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="C121" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="D121" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="E121" t="s">
         <v>4</v>
@@ -7237,13 +7210,13 @@
         <v>101</v>
       </c>
       <c r="B122" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="C122" t="s">
-        <v>525</v>
+        <v>501</v>
       </c>
       <c r="D122" t="s">
-        <v>526</v>
+        <v>1160</v>
       </c>
       <c r="E122" t="s">
         <v>4</v>
@@ -7258,12 +7231,12 @@
         <v>4</v>
       </c>
       <c r="I122" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>842</v>
+        <v>792</v>
       </c>
       <c r="E123" t="s">
         <v>4</v>
@@ -7286,10 +7259,10 @@
         <v>102</v>
       </c>
       <c r="C124" t="s">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="D124" t="s">
-        <v>528</v>
+        <v>503</v>
       </c>
       <c r="E124" t="s">
         <v>4</v>
@@ -7304,7 +7277,7 @@
         <v>4</v>
       </c>
       <c r="I124" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
@@ -7312,13 +7285,13 @@
         <v>103</v>
       </c>
       <c r="B125" t="s">
-        <v>529</v>
+        <v>504</v>
       </c>
       <c r="C125" t="s">
-        <v>529</v>
+        <v>504</v>
       </c>
       <c r="D125" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
       <c r="E125" t="s">
         <v>4</v>
@@ -7341,7 +7314,7 @@
         <v>104</v>
       </c>
       <c r="D126" t="s">
-        <v>531</v>
+        <v>506</v>
       </c>
       <c r="E126" t="s">
         <v>5</v>
@@ -7356,18 +7329,18 @@
         <v>5</v>
       </c>
       <c r="I126" t="s">
-        <v>1186</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>864</v>
+        <v>814</v>
       </c>
       <c r="C127" t="s">
-        <v>1077</v>
+        <v>1026</v>
       </c>
       <c r="D127" t="s">
-        <v>1078</v>
+        <v>1027</v>
       </c>
       <c r="E127" t="s">
         <v>4</v>
@@ -7382,18 +7355,18 @@
         <v>4</v>
       </c>
       <c r="I127" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>865</v>
+        <v>815</v>
       </c>
       <c r="C128" t="s">
-        <v>1079</v>
+        <v>1028</v>
       </c>
       <c r="D128" t="s">
-        <v>1080</v>
+        <v>1029</v>
       </c>
       <c r="E128" t="s">
         <v>4</v>
@@ -7408,7 +7381,7 @@
         <v>4</v>
       </c>
       <c r="I128" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
@@ -7416,10 +7389,10 @@
         <v>105</v>
       </c>
       <c r="C129" t="s">
-        <v>532</v>
+        <v>507</v>
       </c>
       <c r="D129" t="s">
-        <v>533</v>
+        <v>508</v>
       </c>
       <c r="E129" t="s">
         <v>4</v>
@@ -7434,7 +7407,7 @@
         <v>5</v>
       </c>
       <c r="I129" t="s">
-        <v>896</v>
+        <v>846</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
@@ -7442,7 +7415,7 @@
         <v>108</v>
       </c>
       <c r="D130" t="s">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="E130" t="s">
         <v>5</v>
@@ -7485,7 +7458,7 @@
         <v>107</v>
       </c>
       <c r="D132" t="s">
-        <v>534</v>
+        <v>509</v>
       </c>
       <c r="E132" t="s">
         <v>4</v>
@@ -7500,7 +7473,7 @@
         <v>4</v>
       </c>
       <c r="I132" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
@@ -7508,10 +7481,10 @@
         <v>109</v>
       </c>
       <c r="C133" t="s">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="D133" t="s">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="E133" t="s">
         <v>4</v>
@@ -7526,7 +7499,7 @@
         <v>4</v>
       </c>
       <c r="I133" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
@@ -7534,10 +7507,10 @@
         <v>110</v>
       </c>
       <c r="C134" t="s">
-        <v>538</v>
+        <v>513</v>
       </c>
       <c r="D134" t="s">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="E134" t="s">
         <v>4</v>
@@ -7552,7 +7525,7 @@
         <v>4</v>
       </c>
       <c r="I134" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
@@ -7572,7 +7545,7 @@
         <v>4</v>
       </c>
       <c r="I135" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
@@ -7580,10 +7553,10 @@
         <v>112</v>
       </c>
       <c r="C136" t="s">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="D136" t="s">
-        <v>541</v>
+        <v>516</v>
       </c>
       <c r="E136" t="s">
         <v>4</v>
@@ -7598,7 +7571,7 @@
         <v>4</v>
       </c>
       <c r="I136" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
@@ -7606,10 +7579,10 @@
         <v>113</v>
       </c>
       <c r="C137" t="s">
-        <v>542</v>
+        <v>517</v>
       </c>
       <c r="D137" t="s">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="E137" t="s">
         <v>4</v>
@@ -7624,15 +7597,15 @@
         <v>4</v>
       </c>
       <c r="I137" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>908</v>
+        <v>858</v>
       </c>
       <c r="D138" t="s">
-        <v>1127</v>
+        <v>1076</v>
       </c>
       <c r="E138" t="s">
         <v>4</v>
@@ -7655,7 +7628,7 @@
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>544</v>
+        <v>1161</v>
       </c>
       <c r="E139" t="s">
         <v>4</v>
@@ -7670,7 +7643,7 @@
         <v>4</v>
       </c>
       <c r="I139" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
@@ -7678,7 +7651,7 @@
         <v>115</v>
       </c>
       <c r="D140" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="E140" t="s">
         <v>4</v>
@@ -7693,7 +7666,7 @@
         <v>5</v>
       </c>
       <c r="I140" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
@@ -7704,7 +7677,7 @@
         <v>116</v>
       </c>
       <c r="D141" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="E141" t="s">
         <v>4</v>
@@ -7719,7 +7692,7 @@
         <v>5</v>
       </c>
       <c r="I141" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
@@ -7727,7 +7700,7 @@
         <v>117</v>
       </c>
       <c r="D142" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="E142" t="s">
         <v>4</v>
@@ -7750,7 +7723,7 @@
         <v>118</v>
       </c>
       <c r="D143" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="E143" t="s">
         <v>5</v>
@@ -7765,7 +7738,7 @@
         <v>5</v>
       </c>
       <c r="I143" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
@@ -7773,7 +7746,7 @@
         <v>119</v>
       </c>
       <c r="D144" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="E144" t="s">
         <v>4</v>
@@ -7788,7 +7761,7 @@
         <v>4</v>
       </c>
       <c r="I144" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
@@ -7796,10 +7769,10 @@
         <v>120</v>
       </c>
       <c r="C145" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="D145" t="s">
-        <v>825</v>
+        <v>775</v>
       </c>
       <c r="E145" t="s">
         <v>4</v>
@@ -7814,7 +7787,7 @@
         <v>5</v>
       </c>
       <c r="I145" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
@@ -7822,10 +7795,10 @@
         <v>121</v>
       </c>
       <c r="C146" t="s">
-        <v>551</v>
+        <v>525</v>
       </c>
       <c r="D146" t="s">
-        <v>552</v>
+        <v>1162</v>
       </c>
       <c r="E146" t="s">
         <v>4</v>
@@ -7840,18 +7813,18 @@
         <v>4</v>
       </c>
       <c r="I146" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>909</v>
+        <v>859</v>
       </c>
       <c r="B147" t="s">
-        <v>1098</v>
+        <v>1047</v>
       </c>
       <c r="C147" t="s">
-        <v>1098</v>
+        <v>1047</v>
       </c>
       <c r="E147" t="s">
         <v>4</v>
@@ -7871,7 +7844,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>910</v>
+        <v>860</v>
       </c>
       <c r="E148" t="s">
         <v>4</v>
@@ -7914,10 +7887,10 @@
         <v>122</v>
       </c>
       <c r="C150" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="D150" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="E150" t="s">
         <v>4</v>
@@ -7932,7 +7905,7 @@
         <v>4</v>
       </c>
       <c r="I150" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
@@ -7940,10 +7913,10 @@
         <v>123</v>
       </c>
       <c r="C151" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="D151" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="E151" t="s">
         <v>4</v>
@@ -7958,7 +7931,7 @@
         <v>4</v>
       </c>
       <c r="I151" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
@@ -7966,7 +7939,7 @@
         <v>124</v>
       </c>
       <c r="D152" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="E152" t="s">
         <v>4</v>
@@ -8009,10 +7982,10 @@
         <v>125</v>
       </c>
       <c r="C154" t="s">
-        <v>558</v>
+        <v>531</v>
       </c>
       <c r="D154" t="s">
-        <v>559</v>
+        <v>1163</v>
       </c>
       <c r="E154" t="s">
         <v>4</v>
@@ -8027,15 +8000,15 @@
         <v>4</v>
       </c>
       <c r="I154" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>911</v>
+        <v>861</v>
       </c>
       <c r="D155" t="s">
-        <v>1128</v>
+        <v>1077</v>
       </c>
       <c r="E155" t="s">
         <v>4</v>
@@ -8055,7 +8028,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>843</v>
+        <v>793</v>
       </c>
       <c r="E156" t="s">
         <v>4</v>
@@ -8078,10 +8051,10 @@
         <v>128</v>
       </c>
       <c r="C157" t="s">
-        <v>560</v>
+        <v>532</v>
       </c>
       <c r="D157" t="s">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="E157" t="s">
         <v>4</v>
@@ -8096,7 +8069,7 @@
         <v>5</v>
       </c>
       <c r="I157" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
@@ -8124,10 +8097,10 @@
         <v>130</v>
       </c>
       <c r="C159" t="s">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="D159" t="s">
-        <v>563</v>
+        <v>535</v>
       </c>
       <c r="E159" t="s">
         <v>4</v>
@@ -8142,7 +8115,7 @@
         <v>4</v>
       </c>
       <c r="I159" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
@@ -8170,13 +8143,13 @@
         <v>132</v>
       </c>
       <c r="B161" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="C161" t="s">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="D161" t="s">
-        <v>565</v>
+        <v>1164</v>
       </c>
       <c r="E161" t="s">
         <v>4</v>
@@ -8199,7 +8172,7 @@
         <v>133</v>
       </c>
       <c r="D162" t="s">
-        <v>566</v>
+        <v>537</v>
       </c>
       <c r="E162" t="s">
         <v>4</v>
@@ -8214,7 +8187,7 @@
         <v>5</v>
       </c>
       <c r="I162" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
@@ -8242,7 +8215,7 @@
         <v>134</v>
       </c>
       <c r="D164" t="s">
-        <v>567</v>
+        <v>538</v>
       </c>
       <c r="E164" t="s">
         <v>4</v>
@@ -8257,7 +8230,7 @@
         <v>5</v>
       </c>
       <c r="I164" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
@@ -8265,13 +8238,13 @@
         <v>136</v>
       </c>
       <c r="B165" t="s">
-        <v>568</v>
+        <v>539</v>
       </c>
       <c r="C165" t="s">
-        <v>568</v>
+        <v>539</v>
       </c>
       <c r="D165" t="s">
-        <v>569</v>
+        <v>1165</v>
       </c>
       <c r="E165" t="s">
         <v>4</v>
@@ -8286,7 +8259,7 @@
         <v>4</v>
       </c>
       <c r="I165" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
@@ -8294,7 +8267,7 @@
         <v>137</v>
       </c>
       <c r="D166" t="s">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="E166" t="s">
         <v>4</v>
@@ -8317,7 +8290,7 @@
         <v>138</v>
       </c>
       <c r="D167" t="s">
-        <v>616</v>
+        <v>585</v>
       </c>
       <c r="E167" t="s">
         <v>4</v>
@@ -8332,7 +8305,7 @@
         <v>4</v>
       </c>
       <c r="I167" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
@@ -8360,7 +8333,7 @@
         <v>139</v>
       </c>
       <c r="D169" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="E169" t="s">
         <v>4</v>
@@ -8400,10 +8373,10 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>912</v>
+        <v>862</v>
       </c>
       <c r="D171" t="s">
-        <v>1129</v>
+        <v>1078</v>
       </c>
       <c r="E171" t="s">
         <v>4</v>
@@ -8446,10 +8419,10 @@
         <v>143</v>
       </c>
       <c r="C173" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="D173" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
       <c r="E173" t="s">
         <v>4</v>
@@ -8464,7 +8437,7 @@
         <v>4</v>
       </c>
       <c r="I173" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
@@ -8472,7 +8445,7 @@
         <v>144</v>
       </c>
       <c r="D174" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="E174" t="s">
         <v>4</v>
@@ -8495,10 +8468,10 @@
         <v>145</v>
       </c>
       <c r="C175" t="s">
-        <v>575</v>
+        <v>545</v>
       </c>
       <c r="D175" t="s">
-        <v>576</v>
+        <v>1166</v>
       </c>
       <c r="E175" t="s">
         <v>4</v>
@@ -8513,7 +8486,7 @@
         <v>4</v>
       </c>
       <c r="I175" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
@@ -8521,7 +8494,7 @@
         <v>146</v>
       </c>
       <c r="D176" t="s">
-        <v>577</v>
+        <v>546</v>
       </c>
       <c r="E176" t="s">
         <v>4</v>
@@ -8544,7 +8517,7 @@
         <v>147</v>
       </c>
       <c r="D177" t="s">
-        <v>578</v>
+        <v>547</v>
       </c>
       <c r="E177" t="s">
         <v>4</v>
@@ -8564,7 +8537,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>913</v>
+        <v>863</v>
       </c>
       <c r="E178" t="s">
         <v>4</v>
@@ -8587,13 +8560,13 @@
         <v>148</v>
       </c>
       <c r="B179" t="s">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="C179" t="s">
         <v>69</v>
       </c>
       <c r="D179" t="s">
-        <v>580</v>
+        <v>549</v>
       </c>
       <c r="E179" t="s">
         <v>4</v>
@@ -8653,7 +8626,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>914</v>
+        <v>864</v>
       </c>
       <c r="E182" t="s">
         <v>4</v>
@@ -8676,7 +8649,7 @@
         <v>151</v>
       </c>
       <c r="D183" t="s">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="E183" t="s">
         <v>4</v>
@@ -8699,7 +8672,7 @@
         <v>152</v>
       </c>
       <c r="D184" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="E184" t="s">
         <v>4</v>
@@ -8714,7 +8687,7 @@
         <v>5</v>
       </c>
       <c r="I184" t="s">
-        <v>896</v>
+        <v>846</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
@@ -8845,7 +8818,7 @@
         <v>157</v>
       </c>
       <c r="D191" t="s">
-        <v>583</v>
+        <v>552</v>
       </c>
       <c r="E191" t="s">
         <v>5</v>
@@ -8860,7 +8833,7 @@
         <v>5</v>
       </c>
       <c r="I191" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
@@ -8868,10 +8841,10 @@
         <v>158</v>
       </c>
       <c r="C192" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="D192" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="E192" t="s">
         <v>4</v>
@@ -8886,7 +8859,7 @@
         <v>5</v>
       </c>
       <c r="I192" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
@@ -8897,7 +8870,7 @@
         <v>160</v>
       </c>
       <c r="D193" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="E193" t="s">
         <v>5</v>
@@ -8912,7 +8885,7 @@
         <v>5</v>
       </c>
       <c r="I193" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
@@ -8920,7 +8893,7 @@
         <v>161</v>
       </c>
       <c r="D194" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
       <c r="E194" t="s">
         <v>5</v>
@@ -8935,7 +8908,7 @@
         <v>4</v>
       </c>
       <c r="I194" t="s">
-        <v>859</v>
+        <v>809</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
@@ -8960,7 +8933,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>915</v>
+        <v>865</v>
       </c>
       <c r="E196" t="s">
         <v>4</v>
@@ -8980,13 +8953,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>916</v>
+        <v>866</v>
       </c>
       <c r="C197" t="s">
         <v>255</v>
       </c>
       <c r="D197" t="s">
-        <v>1130</v>
+        <v>1079</v>
       </c>
       <c r="E197" t="s">
         <v>4</v>
@@ -9009,7 +8982,7 @@
         <v>164</v>
       </c>
       <c r="D198" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="E198" t="s">
         <v>4</v>
@@ -9049,7 +9022,7 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>917</v>
+        <v>867</v>
       </c>
       <c r="E200" t="s">
         <v>4</v>
@@ -9072,7 +9045,7 @@
         <v>167</v>
       </c>
       <c r="D201" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E201" t="s">
         <v>4</v>
@@ -9087,7 +9060,7 @@
         <v>4</v>
       </c>
       <c r="I201" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
@@ -9095,13 +9068,13 @@
         <v>168</v>
       </c>
       <c r="B202" t="s">
-        <v>592</v>
+        <v>561</v>
       </c>
       <c r="C202" t="s">
-        <v>591</v>
+        <v>560</v>
       </c>
       <c r="D202" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
       <c r="E202" t="s">
         <v>4</v>
@@ -9116,7 +9089,7 @@
         <v>4</v>
       </c>
       <c r="I202" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
@@ -9124,13 +9097,13 @@
         <v>169</v>
       </c>
       <c r="B203" t="s">
-        <v>593</v>
+        <v>562</v>
       </c>
       <c r="C203" t="s">
-        <v>591</v>
+        <v>560</v>
       </c>
       <c r="D203" t="s">
-        <v>594</v>
+        <v>563</v>
       </c>
       <c r="E203" t="s">
         <v>4</v>
@@ -9145,7 +9118,7 @@
         <v>4</v>
       </c>
       <c r="I203" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
@@ -9153,7 +9126,7 @@
         <v>166</v>
       </c>
       <c r="D204" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="E204" t="s">
         <v>5</v>
@@ -9168,7 +9141,7 @@
         <v>5</v>
       </c>
       <c r="I204" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
@@ -9176,13 +9149,13 @@
         <v>170</v>
       </c>
       <c r="B205" t="s">
-        <v>595</v>
+        <v>564</v>
       </c>
       <c r="C205" t="s">
-        <v>595</v>
+        <v>564</v>
       </c>
       <c r="D205" t="s">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="E205" t="s">
         <v>4</v>
@@ -9197,12 +9170,12 @@
         <v>4</v>
       </c>
       <c r="I205" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>918</v>
+        <v>868</v>
       </c>
       <c r="E206" t="s">
         <v>4</v>
@@ -9282,7 +9255,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>919</v>
+        <v>869</v>
       </c>
       <c r="E210" t="s">
         <v>4</v>
@@ -9308,7 +9281,7 @@
         <v>174</v>
       </c>
       <c r="D211" t="s">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="E211" t="s">
         <v>5</v>
@@ -9323,12 +9296,12 @@
         <v>5</v>
       </c>
       <c r="I211" t="s">
-        <v>925</v>
+        <v>875</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>920</v>
+        <v>870</v>
       </c>
       <c r="E212" t="s">
         <v>4</v>
@@ -9348,7 +9321,7 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>921</v>
+        <v>871</v>
       </c>
       <c r="E213" t="s">
         <v>4</v>
@@ -9368,7 +9341,7 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>922</v>
+        <v>872</v>
       </c>
       <c r="E214" t="s">
         <v>4</v>
@@ -9391,7 +9364,7 @@
         <v>177</v>
       </c>
       <c r="D215" t="s">
-        <v>601</v>
+        <v>570</v>
       </c>
       <c r="E215" t="s">
         <v>5</v>
@@ -9406,7 +9379,7 @@
         <v>5</v>
       </c>
       <c r="I215" t="s">
-        <v>898</v>
+        <v>848</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.3">
@@ -9414,7 +9387,7 @@
         <v>175</v>
       </c>
       <c r="D216" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="E216" t="s">
         <v>5</v>
@@ -9437,13 +9410,13 @@
         <v>176</v>
       </c>
       <c r="B217" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="C217" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
       <c r="D217" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="E217" t="s">
         <v>5</v>
@@ -9483,7 +9456,7 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>923</v>
+        <v>873</v>
       </c>
       <c r="E219" t="s">
         <v>4</v>
@@ -9509,7 +9482,7 @@
         <v>180</v>
       </c>
       <c r="D220" t="s">
-        <v>602</v>
+        <v>571</v>
       </c>
       <c r="E220" t="s">
         <v>4</v>
@@ -9524,7 +9497,7 @@
         <v>5</v>
       </c>
       <c r="I220" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.3">
@@ -9532,7 +9505,7 @@
         <v>181</v>
       </c>
       <c r="D221" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="E221" t="s">
         <v>4</v>
@@ -9547,12 +9520,12 @@
         <v>4</v>
       </c>
       <c r="I221" t="s">
-        <v>862</v>
+        <v>812</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>924</v>
+        <v>874</v>
       </c>
       <c r="E222" t="s">
         <v>4</v>
@@ -9581,7 +9554,7 @@
         <v>181</v>
       </c>
       <c r="D223" t="s">
-        <v>605</v>
+        <v>574</v>
       </c>
       <c r="E223" t="s">
         <v>4</v>
@@ -9610,7 +9583,7 @@
         <v>181</v>
       </c>
       <c r="D224" t="s">
-        <v>831</v>
+        <v>781</v>
       </c>
       <c r="E224" t="s">
         <v>5</v>
@@ -9625,7 +9598,7 @@
         <v>4</v>
       </c>
       <c r="I224" t="s">
-        <v>859</v>
+        <v>809</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.3">
@@ -9639,7 +9612,7 @@
         <v>181</v>
       </c>
       <c r="D225" t="s">
-        <v>604</v>
+        <v>573</v>
       </c>
       <c r="E225" t="s">
         <v>5</v>
@@ -9654,18 +9627,18 @@
         <v>5</v>
       </c>
       <c r="I225" t="s">
-        <v>925</v>
+        <v>875</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>866</v>
+        <v>816</v>
       </c>
       <c r="C226" t="s">
-        <v>1081</v>
+        <v>1030</v>
       </c>
       <c r="D226" t="s">
-        <v>1082</v>
+        <v>1031</v>
       </c>
       <c r="E226" t="s">
         <v>4</v>
@@ -9680,7 +9653,7 @@
         <v>5</v>
       </c>
       <c r="I226" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.3">
@@ -9705,7 +9678,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>926</v>
+        <v>876</v>
       </c>
       <c r="E228" t="s">
         <v>4</v>
@@ -9748,10 +9721,10 @@
         <v>186</v>
       </c>
       <c r="B230" t="s">
-        <v>606</v>
+        <v>575</v>
       </c>
       <c r="C230" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="E230" t="s">
         <v>4</v>
@@ -9771,7 +9744,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>927</v>
+        <v>877</v>
       </c>
       <c r="E231" t="s">
         <v>4</v>
@@ -9791,7 +9764,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>928</v>
+        <v>878</v>
       </c>
       <c r="E232" t="s">
         <v>4</v>
@@ -9846,7 +9819,7 @@
         <v>4</v>
       </c>
       <c r="I234" t="s">
-        <v>621</v>
+        <v>590</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.3">
@@ -9871,7 +9844,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>929</v>
+        <v>879</v>
       </c>
       <c r="E236" t="s">
         <v>4</v>
@@ -9914,7 +9887,7 @@
         <v>191</v>
       </c>
       <c r="D238" t="s">
-        <v>608</v>
+        <v>577</v>
       </c>
       <c r="E238" t="s">
         <v>4</v>
@@ -9929,7 +9902,7 @@
         <v>5</v>
       </c>
       <c r="I238" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.3">
@@ -9969,7 +9942,7 @@
         <v>4</v>
       </c>
       <c r="I240" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.3">
@@ -9977,7 +9950,7 @@
         <v>194</v>
       </c>
       <c r="D241" t="s">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="E241" t="s">
         <v>4</v>
@@ -10032,7 +10005,7 @@
         <v>5</v>
       </c>
       <c r="I243" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.3">
@@ -10052,7 +10025,7 @@
         <v>4</v>
       </c>
       <c r="I244" t="s">
-        <v>859</v>
+        <v>809</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.3">
@@ -10077,10 +10050,10 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>844</v>
+        <v>794</v>
       </c>
       <c r="D246" t="s">
-        <v>1083</v>
+        <v>1032</v>
       </c>
       <c r="E246" t="s">
         <v>4</v>
@@ -10100,13 +10073,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>867</v>
+        <v>817</v>
       </c>
       <c r="C247" t="s">
-        <v>1084</v>
+        <v>1033</v>
       </c>
       <c r="D247" t="s">
-        <v>1085</v>
+        <v>1034</v>
       </c>
       <c r="E247" t="s">
         <v>4</v>
@@ -10121,7 +10094,7 @@
         <v>4</v>
       </c>
       <c r="I247" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.3">
@@ -10129,7 +10102,7 @@
         <v>199</v>
       </c>
       <c r="D248" t="s">
-        <v>610</v>
+        <v>579</v>
       </c>
       <c r="E248" t="s">
         <v>4</v>
@@ -10144,7 +10117,7 @@
         <v>4</v>
       </c>
       <c r="I248" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.3">
@@ -10184,7 +10157,7 @@
         <v>4</v>
       </c>
       <c r="I250" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.3">
@@ -10232,7 +10205,7 @@
         <v>204</v>
       </c>
       <c r="D253" t="s">
-        <v>832</v>
+        <v>782</v>
       </c>
       <c r="E253" t="s">
         <v>5</v>
@@ -10267,7 +10240,7 @@
         <v>4</v>
       </c>
       <c r="I254" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.3">
@@ -10275,7 +10248,7 @@
         <v>206</v>
       </c>
       <c r="D255" t="s">
-        <v>611</v>
+        <v>580</v>
       </c>
       <c r="E255" t="s">
         <v>5</v>
@@ -10290,7 +10263,7 @@
         <v>5</v>
       </c>
       <c r="I255" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.3">
@@ -10310,18 +10283,18 @@
         <v>5</v>
       </c>
       <c r="I256" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>868</v>
+        <v>818</v>
       </c>
       <c r="C257" t="s">
-        <v>1086</v>
+        <v>1035</v>
       </c>
       <c r="D257" t="s">
-        <v>1087</v>
+        <v>1036</v>
       </c>
       <c r="E257" t="s">
         <v>4</v>
@@ -10336,7 +10309,7 @@
         <v>4</v>
       </c>
       <c r="I257" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.3">
@@ -10356,7 +10329,7 @@
         <v>5</v>
       </c>
       <c r="I258" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.3">
@@ -10364,13 +10337,13 @@
         <v>209</v>
       </c>
       <c r="B259" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="C259" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="D259" t="s">
-        <v>612</v>
+        <v>581</v>
       </c>
       <c r="E259" t="s">
         <v>4</v>
@@ -10385,7 +10358,7 @@
         <v>5</v>
       </c>
       <c r="I259" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.3">
@@ -10405,7 +10378,7 @@
         <v>4</v>
       </c>
       <c r="I260" t="s">
-        <v>862</v>
+        <v>812</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.3">
@@ -10413,7 +10386,7 @@
         <v>211</v>
       </c>
       <c r="D261" t="s">
-        <v>613</v>
+        <v>582</v>
       </c>
       <c r="E261" t="s">
         <v>4</v>
@@ -10428,7 +10401,7 @@
         <v>5</v>
       </c>
       <c r="I261" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.3">
@@ -10436,10 +10409,10 @@
         <v>212</v>
       </c>
       <c r="C262" t="s">
-        <v>614</v>
+        <v>583</v>
       </c>
       <c r="D262" t="s">
-        <v>615</v>
+        <v>584</v>
       </c>
       <c r="E262" t="s">
         <v>4</v>
@@ -10454,7 +10427,7 @@
         <v>5</v>
       </c>
       <c r="I262" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.3">
@@ -10479,16 +10452,16 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>1132</v>
+        <v>1081</v>
       </c>
       <c r="B264" t="s">
-        <v>1131</v>
+        <v>1080</v>
       </c>
       <c r="C264" t="s">
-        <v>1131</v>
+        <v>1080</v>
       </c>
       <c r="D264" t="s">
-        <v>1133</v>
+        <v>1082</v>
       </c>
       <c r="E264" t="s">
         <v>4</v>
@@ -10543,7 +10516,7 @@
         <v>5</v>
       </c>
       <c r="I266" t="s">
-        <v>898</v>
+        <v>848</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.3">
@@ -10551,10 +10524,10 @@
         <v>216</v>
       </c>
       <c r="B267" t="s">
-        <v>739</v>
+        <v>700</v>
       </c>
       <c r="C267" t="s">
-        <v>739</v>
+        <v>700</v>
       </c>
       <c r="E267" t="s">
         <v>4</v>
@@ -10594,7 +10567,7 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>930</v>
+        <v>880</v>
       </c>
       <c r="E269" t="s">
         <v>4</v>
@@ -10617,7 +10590,7 @@
         <v>218</v>
       </c>
       <c r="D270" t="s">
-        <v>671</v>
+        <v>640</v>
       </c>
       <c r="E270" t="s">
         <v>4</v>
@@ -10632,7 +10605,7 @@
         <v>4</v>
       </c>
       <c r="I270" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.3">
@@ -10640,7 +10613,7 @@
         <v>219</v>
       </c>
       <c r="D271" t="s">
-        <v>672</v>
+        <v>641</v>
       </c>
       <c r="E271" t="s">
         <v>4</v>
@@ -10655,7 +10628,7 @@
         <v>4</v>
       </c>
       <c r="I271" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.3">
@@ -10666,7 +10639,7 @@
         <v>220</v>
       </c>
       <c r="D272" t="s">
-        <v>740</v>
+        <v>701</v>
       </c>
       <c r="E272" t="s">
         <v>4</v>
@@ -10681,7 +10654,7 @@
         <v>5</v>
       </c>
       <c r="I272" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.3">
@@ -10692,7 +10665,7 @@
         <v>221</v>
       </c>
       <c r="D273" t="s">
-        <v>741</v>
+        <v>702</v>
       </c>
       <c r="E273" t="s">
         <v>4</v>
@@ -10707,7 +10680,7 @@
         <v>5</v>
       </c>
       <c r="I273" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.3">
@@ -10738,7 +10711,7 @@
         <v>223</v>
       </c>
       <c r="D275" t="s">
-        <v>742</v>
+        <v>703</v>
       </c>
       <c r="E275" t="s">
         <v>4</v>
@@ -10753,7 +10726,7 @@
         <v>4</v>
       </c>
       <c r="I275" t="s">
-        <v>618</v>
+        <v>587</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.3">
@@ -10761,7 +10734,7 @@
         <v>224</v>
       </c>
       <c r="D276" t="s">
-        <v>743</v>
+        <v>704</v>
       </c>
       <c r="E276" t="s">
         <v>4</v>
@@ -10776,12 +10749,12 @@
         <v>4</v>
       </c>
       <c r="I276" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>931</v>
+        <v>881</v>
       </c>
       <c r="E277" t="s">
         <v>4</v>
@@ -10804,7 +10777,7 @@
         <v>225</v>
       </c>
       <c r="D278" t="s">
-        <v>744</v>
+        <v>705</v>
       </c>
       <c r="E278" t="s">
         <v>4</v>
@@ -10827,7 +10800,7 @@
         <v>226</v>
       </c>
       <c r="D279" t="s">
-        <v>673</v>
+        <v>642</v>
       </c>
       <c r="E279" t="s">
         <v>4</v>
@@ -10850,10 +10823,10 @@
         <v>227</v>
       </c>
       <c r="C280" t="s">
-        <v>623</v>
+        <v>592</v>
       </c>
       <c r="D280" t="s">
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="E280" t="s">
         <v>4</v>
@@ -10868,12 +10841,12 @@
         <v>4</v>
       </c>
       <c r="I280" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>932</v>
+        <v>882</v>
       </c>
       <c r="E281" t="s">
         <v>4</v>
@@ -10899,7 +10872,7 @@
         <v>228</v>
       </c>
       <c r="D282" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="E282" t="s">
         <v>5</v>
@@ -10959,7 +10932,7 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>933</v>
+        <v>883</v>
       </c>
       <c r="E285" t="s">
         <v>4</v>
@@ -10979,7 +10952,7 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>934</v>
+        <v>884</v>
       </c>
       <c r="E286" t="s">
         <v>4</v>
@@ -11019,7 +10992,7 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>935</v>
+        <v>885</v>
       </c>
       <c r="E288" t="s">
         <v>4</v>
@@ -11039,7 +11012,7 @@
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>936</v>
+        <v>886</v>
       </c>
       <c r="E289" t="s">
         <v>4</v>
@@ -11059,7 +11032,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>937</v>
+        <v>887</v>
       </c>
       <c r="E290" t="s">
         <v>4</v>
@@ -11079,7 +11052,7 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>828</v>
+        <v>778</v>
       </c>
       <c r="E291" t="s">
         <v>5</v>
@@ -11099,10 +11072,10 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>833</v>
+        <v>783</v>
       </c>
       <c r="D292" t="s">
-        <v>1088</v>
+        <v>1037</v>
       </c>
       <c r="E292" t="s">
         <v>5</v>
@@ -11117,7 +11090,7 @@
         <v>5</v>
       </c>
       <c r="I292" t="s">
-        <v>898</v>
+        <v>848</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.3">
@@ -11142,7 +11115,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="E294" t="s">
         <v>4</v>
@@ -11165,7 +11138,7 @@
         <v>233</v>
       </c>
       <c r="D295" t="s">
-        <v>674</v>
+        <v>643</v>
       </c>
       <c r="E295" t="s">
         <v>4</v>
@@ -11228,7 +11201,7 @@
         <v>235</v>
       </c>
       <c r="D298" t="s">
-        <v>747</v>
+        <v>708</v>
       </c>
       <c r="E298" t="s">
         <v>5</v>
@@ -11243,7 +11216,7 @@
         <v>5</v>
       </c>
       <c r="I298" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.3">
@@ -11251,13 +11224,13 @@
         <v>437</v>
       </c>
       <c r="B299" t="s">
-        <v>748</v>
+        <v>709</v>
       </c>
       <c r="C299" t="s">
-        <v>624</v>
+        <v>593</v>
       </c>
       <c r="D299" t="s">
-        <v>749</v>
+        <v>710</v>
       </c>
       <c r="E299" t="s">
         <v>4</v>
@@ -11272,7 +11245,7 @@
         <v>4</v>
       </c>
       <c r="I299" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
@@ -11300,10 +11273,10 @@
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>939</v>
+        <v>889</v>
       </c>
       <c r="D301" t="s">
-        <v>1134</v>
+        <v>1083</v>
       </c>
       <c r="E301" t="s">
         <v>4</v>
@@ -11326,10 +11299,10 @@
         <v>238</v>
       </c>
       <c r="C302" t="s">
-        <v>625</v>
+        <v>594</v>
       </c>
       <c r="D302" t="s">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="E302" t="s">
         <v>4</v>
@@ -11344,12 +11317,12 @@
         <v>5</v>
       </c>
       <c r="I302" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>1089</v>
+        <v>1038</v>
       </c>
       <c r="E303" t="s">
         <v>4</v>
@@ -11369,7 +11342,7 @@
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>940</v>
+        <v>890</v>
       </c>
       <c r="E304" t="s">
         <v>4</v>
@@ -11389,7 +11362,7 @@
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>941</v>
+        <v>891</v>
       </c>
       <c r="E305" t="s">
         <v>4</v>
@@ -11409,7 +11382,7 @@
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>942</v>
+        <v>892</v>
       </c>
       <c r="E306" t="s">
         <v>4</v>
@@ -11429,7 +11402,7 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>869</v>
+        <v>819</v>
       </c>
       <c r="E307" t="s">
         <v>4</v>
@@ -11444,7 +11417,7 @@
         <v>5</v>
       </c>
       <c r="I307" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.3">
@@ -11452,7 +11425,7 @@
         <v>239</v>
       </c>
       <c r="D308" t="s">
-        <v>676</v>
+        <v>1167</v>
       </c>
       <c r="E308" t="s">
         <v>4</v>
@@ -11467,15 +11440,15 @@
         <v>5</v>
       </c>
       <c r="I308" t="s">
-        <v>964</v>
+        <v>914</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>943</v>
+        <v>893</v>
       </c>
       <c r="D309" t="s">
-        <v>1135</v>
+        <v>1084</v>
       </c>
       <c r="E309" t="s">
         <v>4</v>
@@ -11495,7 +11468,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>944</v>
+        <v>894</v>
       </c>
       <c r="E310" t="s">
         <v>4</v>
@@ -11518,7 +11491,7 @@
         <v>240</v>
       </c>
       <c r="D311" t="s">
-        <v>677</v>
+        <v>645</v>
       </c>
       <c r="E311" t="s">
         <v>4</v>
@@ -11533,7 +11506,7 @@
         <v>5</v>
       </c>
       <c r="I311" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.3">
@@ -11541,10 +11514,7 @@
         <v>241</v>
       </c>
       <c r="C312" t="s">
-        <v>750</v>
-      </c>
-      <c r="D312" t="s">
-        <v>678</v>
+        <v>711</v>
       </c>
       <c r="E312" t="s">
         <v>4</v>
@@ -11567,7 +11537,7 @@
         <v>242</v>
       </c>
       <c r="D313" t="s">
-        <v>679</v>
+        <v>1168</v>
       </c>
       <c r="E313" t="s">
         <v>4</v>
@@ -11582,15 +11552,15 @@
         <v>4</v>
       </c>
       <c r="I313" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>945</v>
+        <v>895</v>
       </c>
       <c r="D314" t="s">
-        <v>1136</v>
+        <v>1085</v>
       </c>
       <c r="E314" t="s">
         <v>4</v>
@@ -11613,7 +11583,7 @@
         <v>243</v>
       </c>
       <c r="D315" t="s">
-        <v>751</v>
+        <v>712</v>
       </c>
       <c r="E315" t="s">
         <v>4</v>
@@ -11628,7 +11598,7 @@
         <v>5</v>
       </c>
       <c r="I315" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.3">
@@ -11636,10 +11606,10 @@
         <v>244</v>
       </c>
       <c r="C316" t="s">
-        <v>752</v>
+        <v>713</v>
       </c>
       <c r="D316" t="s">
-        <v>753</v>
+        <v>714</v>
       </c>
       <c r="E316" t="s">
         <v>4</v>
@@ -11654,7 +11624,7 @@
         <v>4</v>
       </c>
       <c r="I316" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.3">
@@ -11674,12 +11644,12 @@
         <v>4</v>
       </c>
       <c r="I317" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>946</v>
+        <v>896</v>
       </c>
       <c r="E318" t="s">
         <v>4</v>
@@ -11699,16 +11669,16 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>834</v>
+        <v>784</v>
       </c>
       <c r="B319" t="s">
-        <v>1092</v>
+        <v>1041</v>
       </c>
       <c r="C319" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="D319" t="s">
-        <v>1093</v>
+        <v>1042</v>
       </c>
       <c r="E319" t="s">
         <v>5</v>
@@ -11723,7 +11693,7 @@
         <v>5</v>
       </c>
       <c r="I319" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.3">
@@ -11731,10 +11701,10 @@
         <v>246</v>
       </c>
       <c r="C320" t="s">
-        <v>626</v>
+        <v>595</v>
       </c>
       <c r="D320" t="s">
-        <v>680</v>
+        <v>646</v>
       </c>
       <c r="E320" t="s">
         <v>4</v>
@@ -11749,12 +11719,12 @@
         <v>4</v>
       </c>
       <c r="I320" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>948</v>
+        <v>898</v>
       </c>
       <c r="E321" t="s">
         <v>4</v>
@@ -11774,16 +11744,16 @@
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>845</v>
+        <v>795</v>
       </c>
       <c r="B322" t="s">
-        <v>1090</v>
+        <v>1039</v>
       </c>
       <c r="C322" t="s">
-        <v>1090</v>
+        <v>1039</v>
       </c>
       <c r="D322" t="s">
-        <v>1091</v>
+        <v>1040</v>
       </c>
       <c r="E322" t="s">
         <v>4</v>
@@ -11798,7 +11768,7 @@
         <v>5</v>
       </c>
       <c r="I322" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.3">
@@ -11818,12 +11788,12 @@
         <v>4</v>
       </c>
       <c r="I323" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>947</v>
+        <v>897</v>
       </c>
       <c r="E324" t="s">
         <v>4</v>
@@ -11846,10 +11816,10 @@
         <v>248</v>
       </c>
       <c r="C325" t="s">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="D325" t="s">
-        <v>754</v>
+        <v>715</v>
       </c>
       <c r="E325" t="s">
         <v>4</v>
@@ -11864,7 +11834,7 @@
         <v>5</v>
       </c>
       <c r="I325" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.3">
@@ -11872,13 +11842,13 @@
         <v>249</v>
       </c>
       <c r="B326" t="s">
-        <v>628</v>
+        <v>597</v>
       </c>
       <c r="C326" t="s">
-        <v>629</v>
+        <v>598</v>
       </c>
       <c r="D326" t="s">
-        <v>681</v>
+        <v>647</v>
       </c>
       <c r="E326" t="s">
         <v>4</v>
@@ -11893,7 +11863,7 @@
         <v>5</v>
       </c>
       <c r="I326" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.3">
@@ -11901,7 +11871,7 @@
         <v>250</v>
       </c>
       <c r="D327" t="s">
-        <v>1166</v>
+        <v>1115</v>
       </c>
       <c r="E327" t="s">
         <v>4</v>
@@ -11921,10 +11891,10 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>949</v>
+        <v>899</v>
       </c>
       <c r="D328" t="s">
-        <v>1137</v>
+        <v>1086</v>
       </c>
       <c r="E328" t="s">
         <v>4</v>
@@ -11947,7 +11917,7 @@
         <v>251</v>
       </c>
       <c r="D329" t="s">
-        <v>755</v>
+        <v>716</v>
       </c>
       <c r="E329" t="s">
         <v>4</v>
@@ -11970,7 +11940,7 @@
         <v>252</v>
       </c>
       <c r="D330" t="s">
-        <v>827</v>
+        <v>777</v>
       </c>
       <c r="E330" t="s">
         <v>4</v>
@@ -12013,7 +11983,7 @@
         <v>254</v>
       </c>
       <c r="D332" t="s">
-        <v>682</v>
+        <v>648</v>
       </c>
       <c r="E332" t="s">
         <v>4</v>
@@ -12028,15 +11998,15 @@
         <v>4</v>
       </c>
       <c r="I332" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="D333" t="s">
-        <v>1138</v>
+        <v>1087</v>
       </c>
       <c r="E333" t="s">
         <v>4</v>
@@ -12056,7 +12026,7 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>951</v>
+        <v>901</v>
       </c>
       <c r="E334" t="s">
         <v>4</v>
@@ -12079,7 +12049,7 @@
         <v>255</v>
       </c>
       <c r="D335" t="s">
-        <v>756</v>
+        <v>717</v>
       </c>
       <c r="E335" t="s">
         <v>5</v>
@@ -12102,10 +12072,10 @@
         <v>256</v>
       </c>
       <c r="B336" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="C336" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="E336" t="s">
         <v>5</v>
@@ -12128,7 +12098,7 @@
         <v>257</v>
       </c>
       <c r="D337" t="s">
-        <v>683</v>
+        <v>649</v>
       </c>
       <c r="E337" t="s">
         <v>4</v>
@@ -12151,7 +12121,7 @@
         <v>258</v>
       </c>
       <c r="D338" t="s">
-        <v>684</v>
+        <v>650</v>
       </c>
       <c r="E338" t="s">
         <v>5</v>
@@ -12171,7 +12141,7 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>952</v>
+        <v>902</v>
       </c>
       <c r="E339" t="s">
         <v>4</v>
@@ -12194,7 +12164,7 @@
         <v>259</v>
       </c>
       <c r="D340" t="s">
-        <v>685</v>
+        <v>651</v>
       </c>
       <c r="E340" t="s">
         <v>4</v>
@@ -12217,7 +12187,7 @@
         <v>260</v>
       </c>
       <c r="D341" t="s">
-        <v>757</v>
+        <v>718</v>
       </c>
       <c r="E341" t="s">
         <v>4</v>
@@ -12232,7 +12202,7 @@
         <v>5</v>
       </c>
       <c r="I341" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.3">
@@ -12240,13 +12210,13 @@
         <v>261</v>
       </c>
       <c r="B342" t="s">
-        <v>630</v>
+        <v>599</v>
       </c>
       <c r="C342" t="s">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="D342" t="s">
-        <v>758</v>
+        <v>1169</v>
       </c>
       <c r="E342" t="s">
         <v>4</v>
@@ -12266,10 +12236,10 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>870</v>
+        <v>820</v>
       </c>
       <c r="D343" t="s">
-        <v>1094</v>
+        <v>1043</v>
       </c>
       <c r="E343" t="s">
         <v>4</v>
@@ -12284,15 +12254,15 @@
         <v>4</v>
       </c>
       <c r="I343" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>953</v>
+        <v>903</v>
       </c>
       <c r="D344" t="s">
-        <v>759</v>
+        <v>719</v>
       </c>
       <c r="E344" t="s">
         <v>4</v>
@@ -12312,7 +12282,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>954</v>
+        <v>904</v>
       </c>
       <c r="E345" t="s">
         <v>4</v>
@@ -12335,7 +12305,7 @@
         <v>262</v>
       </c>
       <c r="D346" t="s">
-        <v>686</v>
+        <v>652</v>
       </c>
       <c r="E346" t="s">
         <v>4</v>
@@ -12355,7 +12325,7 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>955</v>
+        <v>905</v>
       </c>
       <c r="E347" t="s">
         <v>4</v>
@@ -12384,7 +12354,7 @@
         <v>325</v>
       </c>
       <c r="D348" t="s">
-        <v>687</v>
+        <v>653</v>
       </c>
       <c r="E348" t="s">
         <v>4</v>
@@ -12404,7 +12374,7 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>956</v>
+        <v>906</v>
       </c>
       <c r="E349" t="s">
         <v>4</v>
@@ -12444,7 +12414,7 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>957</v>
+        <v>907</v>
       </c>
       <c r="E351" t="s">
         <v>4</v>
@@ -12464,7 +12434,7 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>958</v>
+        <v>908</v>
       </c>
       <c r="E352" t="s">
         <v>4</v>
@@ -12487,7 +12457,7 @@
         <v>265</v>
       </c>
       <c r="D353" t="s">
-        <v>688</v>
+        <v>654</v>
       </c>
       <c r="E353" t="s">
         <v>5</v>
@@ -12502,12 +12472,12 @@
         <v>5</v>
       </c>
       <c r="I353" t="s">
-        <v>925</v>
+        <v>875</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>959</v>
+        <v>909</v>
       </c>
       <c r="E354" t="s">
         <v>4</v>
@@ -12530,7 +12500,7 @@
         <v>266</v>
       </c>
       <c r="D355" t="s">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="E355" t="s">
         <v>5</v>
@@ -12545,18 +12515,18 @@
         <v>5</v>
       </c>
       <c r="I355" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>871</v>
+        <v>821</v>
       </c>
       <c r="C356" t="s">
-        <v>871</v>
+        <v>821</v>
       </c>
       <c r="D356" t="s">
-        <v>1095</v>
+        <v>1044</v>
       </c>
       <c r="E356" t="s">
         <v>4</v>
@@ -12571,12 +12541,12 @@
         <v>4</v>
       </c>
       <c r="I356" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>960</v>
+        <v>910</v>
       </c>
       <c r="E357" t="s">
         <v>4</v>
@@ -12596,10 +12566,10 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>961</v>
+        <v>911</v>
       </c>
       <c r="D358" t="s">
-        <v>761</v>
+        <v>721</v>
       </c>
       <c r="E358" t="s">
         <v>4</v>
@@ -12622,10 +12592,10 @@
         <v>267</v>
       </c>
       <c r="B359" t="s">
-        <v>632</v>
+        <v>601</v>
       </c>
       <c r="C359" t="s">
-        <v>632</v>
+        <v>601</v>
       </c>
       <c r="E359" t="s">
         <v>4</v>
@@ -12645,7 +12615,7 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>846</v>
+        <v>796</v>
       </c>
       <c r="E360" t="s">
         <v>4</v>
@@ -12668,7 +12638,7 @@
         <v>268</v>
       </c>
       <c r="D361" t="s">
-        <v>689</v>
+        <v>655</v>
       </c>
       <c r="E361" t="s">
         <v>4</v>
@@ -12683,7 +12653,7 @@
         <v>4</v>
       </c>
       <c r="I361" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.3">
@@ -12708,13 +12678,13 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>962</v>
+        <v>912</v>
       </c>
       <c r="B363" t="s">
-        <v>1139</v>
+        <v>1088</v>
       </c>
       <c r="D363" t="s">
-        <v>1140</v>
+        <v>1089</v>
       </c>
       <c r="E363" t="s">
         <v>4</v>
@@ -12737,7 +12707,7 @@
         <v>270</v>
       </c>
       <c r="D364" t="s">
-        <v>762</v>
+        <v>722</v>
       </c>
       <c r="E364" t="s">
         <v>4</v>
@@ -12752,21 +12722,21 @@
         <v>4</v>
       </c>
       <c r="I364" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>963</v>
+        <v>913</v>
       </c>
       <c r="B365" t="s">
-        <v>1141</v>
+        <v>1090</v>
       </c>
       <c r="C365" t="s">
-        <v>1141</v>
+        <v>1090</v>
       </c>
       <c r="D365" t="s">
-        <v>1142</v>
+        <v>1091</v>
       </c>
       <c r="E365" t="s">
         <v>4</v>
@@ -12792,7 +12762,7 @@
         <v>271</v>
       </c>
       <c r="D366" t="s">
-        <v>965</v>
+        <v>915</v>
       </c>
       <c r="E366" t="s">
         <v>4</v>
@@ -12807,18 +12777,18 @@
         <v>5</v>
       </c>
       <c r="I366" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>1144</v>
+        <v>1093</v>
       </c>
       <c r="B367" t="s">
-        <v>1143</v>
+        <v>1092</v>
       </c>
       <c r="C367" t="s">
-        <v>1143</v>
+        <v>1092</v>
       </c>
       <c r="E367" t="s">
         <v>4</v>
@@ -12841,7 +12811,7 @@
         <v>272</v>
       </c>
       <c r="D368" t="s">
-        <v>690</v>
+        <v>656</v>
       </c>
       <c r="E368" t="s">
         <v>4</v>
@@ -12856,7 +12826,7 @@
         <v>5</v>
       </c>
       <c r="I368" t="s">
-        <v>964</v>
+        <v>914</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.3">
@@ -12864,10 +12834,10 @@
         <v>273</v>
       </c>
       <c r="C369" t="s">
-        <v>763</v>
+        <v>723</v>
       </c>
       <c r="D369" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="E369" t="s">
         <v>4</v>
@@ -12882,7 +12852,7 @@
         <v>4</v>
       </c>
       <c r="I369" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.3">
@@ -12890,7 +12860,7 @@
         <v>274</v>
       </c>
       <c r="D370" t="s">
-        <v>691</v>
+        <v>657</v>
       </c>
       <c r="E370" t="s">
         <v>4</v>
@@ -12905,7 +12875,7 @@
         <v>5</v>
       </c>
       <c r="I370" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.3">
@@ -12916,7 +12886,7 @@
         <v>275</v>
       </c>
       <c r="D371" t="s">
-        <v>692</v>
+        <v>658</v>
       </c>
       <c r="E371" t="s">
         <v>4</v>
@@ -12931,12 +12901,12 @@
         <v>5</v>
       </c>
       <c r="I371" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>966</v>
+        <v>916</v>
       </c>
       <c r="E372" t="s">
         <v>4</v>
@@ -12956,10 +12926,10 @@
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>967</v>
+        <v>917</v>
       </c>
       <c r="C373" t="s">
-        <v>1145</v>
+        <v>1094</v>
       </c>
       <c r="E373" t="s">
         <v>4</v>
@@ -12979,7 +12949,7 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>835</v>
+        <v>785</v>
       </c>
       <c r="E374" t="s">
         <v>5</v>
@@ -13002,7 +12972,7 @@
         <v>276</v>
       </c>
       <c r="D375" t="s">
-        <v>693</v>
+        <v>659</v>
       </c>
       <c r="E375" t="s">
         <v>4</v>
@@ -13017,7 +12987,7 @@
         <v>4</v>
       </c>
       <c r="I375" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.3">
@@ -13042,7 +13012,7 @@
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>968</v>
+        <v>918</v>
       </c>
       <c r="E377" t="s">
         <v>4</v>
@@ -13062,7 +13032,7 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>969</v>
+        <v>919</v>
       </c>
       <c r="E378" t="s">
         <v>4</v>
@@ -13082,7 +13052,7 @@
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>970</v>
+        <v>920</v>
       </c>
       <c r="E379" t="s">
         <v>4</v>
@@ -13102,7 +13072,7 @@
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>971</v>
+        <v>921</v>
       </c>
       <c r="E380" t="s">
         <v>4</v>
@@ -13142,7 +13112,7 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>972</v>
+        <v>922</v>
       </c>
       <c r="E382" t="s">
         <v>4</v>
@@ -13165,7 +13135,7 @@
         <v>279</v>
       </c>
       <c r="D383" t="s">
-        <v>694</v>
+        <v>660</v>
       </c>
       <c r="E383" t="s">
         <v>4</v>
@@ -13180,12 +13150,12 @@
         <v>5</v>
       </c>
       <c r="I383" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="E384" t="s">
         <v>4</v>
@@ -13208,10 +13178,10 @@
         <v>280</v>
       </c>
       <c r="C385" t="s">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="D385" t="s">
-        <v>765</v>
+        <v>725</v>
       </c>
       <c r="E385" t="s">
         <v>4</v>
@@ -13226,12 +13196,12 @@
         <v>5</v>
       </c>
       <c r="I385" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>974</v>
+        <v>924</v>
       </c>
       <c r="E386" t="s">
         <v>4</v>
@@ -13297,10 +13267,10 @@
         <v>209</v>
       </c>
       <c r="C389" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="D389" t="s">
-        <v>695</v>
+        <v>661</v>
       </c>
       <c r="E389" t="s">
         <v>5</v>
@@ -13315,12 +13285,12 @@
         <v>5</v>
       </c>
       <c r="I389" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>975</v>
+        <v>925</v>
       </c>
       <c r="E390" t="s">
         <v>4</v>
@@ -13343,7 +13313,7 @@
         <v>284</v>
       </c>
       <c r="D391" t="s">
-        <v>836</v>
+        <v>786</v>
       </c>
       <c r="E391" t="s">
         <v>5</v>
@@ -13358,7 +13328,7 @@
         <v>5</v>
       </c>
       <c r="I391" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.3">
@@ -13366,13 +13336,13 @@
         <v>285</v>
       </c>
       <c r="B392" t="s">
-        <v>634</v>
+        <v>603</v>
       </c>
       <c r="C392" t="s">
-        <v>634</v>
+        <v>603</v>
       </c>
       <c r="D392" t="s">
-        <v>766</v>
+        <v>1170</v>
       </c>
       <c r="E392" t="s">
         <v>4</v>
@@ -13387,18 +13357,18 @@
         <v>4</v>
       </c>
       <c r="I392" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>976</v>
+        <v>926</v>
       </c>
       <c r="B393" t="s">
-        <v>1146</v>
+        <v>1095</v>
       </c>
       <c r="D393" t="s">
-        <v>1147</v>
+        <v>1096</v>
       </c>
       <c r="E393" t="s">
         <v>4</v>
@@ -13453,7 +13423,7 @@
         <v>4</v>
       </c>
       <c r="I395" t="s">
-        <v>862</v>
+        <v>812</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.3">
@@ -13461,10 +13431,10 @@
         <v>288</v>
       </c>
       <c r="C396" t="s">
-        <v>635</v>
+        <v>604</v>
       </c>
       <c r="D396" t="s">
-        <v>696</v>
+        <v>662</v>
       </c>
       <c r="E396" t="s">
         <v>4</v>
@@ -13479,12 +13449,12 @@
         <v>5</v>
       </c>
       <c r="I396" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>977</v>
+        <v>927</v>
       </c>
       <c r="E397" t="s">
         <v>4</v>
@@ -13504,7 +13474,7 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>978</v>
+        <v>928</v>
       </c>
       <c r="E398" t="s">
         <v>4</v>
@@ -13527,13 +13497,13 @@
         <v>289</v>
       </c>
       <c r="B399" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="C399" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
       <c r="D399" t="s">
-        <v>767</v>
+        <v>726</v>
       </c>
       <c r="E399" t="s">
         <v>5</v>
@@ -13559,7 +13529,7 @@
         <v>290</v>
       </c>
       <c r="D400" t="s">
-        <v>697</v>
+        <v>663</v>
       </c>
       <c r="E400" t="s">
         <v>4</v>
@@ -13574,21 +13544,21 @@
         <v>5</v>
       </c>
       <c r="I400" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>979</v>
+        <v>929</v>
       </c>
       <c r="B401" t="s">
-        <v>1148</v>
+        <v>1097</v>
       </c>
       <c r="C401" t="s">
-        <v>1148</v>
+        <v>1097</v>
       </c>
       <c r="D401" t="s">
-        <v>1149</v>
+        <v>1098</v>
       </c>
       <c r="E401" t="s">
         <v>4</v>
@@ -13629,7 +13599,7 @@
         <v>5</v>
       </c>
       <c r="I402" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.3">
@@ -13637,7 +13607,7 @@
         <v>291</v>
       </c>
       <c r="D403" t="s">
-        <v>698</v>
+        <v>664</v>
       </c>
       <c r="E403" t="s">
         <v>4</v>
@@ -13652,7 +13622,7 @@
         <v>4</v>
       </c>
       <c r="I403" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.3">
@@ -13677,7 +13647,7 @@
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>847</v>
+        <v>797</v>
       </c>
       <c r="E405" t="s">
         <v>4</v>
@@ -13697,7 +13667,7 @@
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>980</v>
+        <v>930</v>
       </c>
       <c r="E406" t="s">
         <v>4</v>
@@ -13720,10 +13690,10 @@
         <v>295</v>
       </c>
       <c r="B407" t="s">
-        <v>636</v>
+        <v>605</v>
       </c>
       <c r="C407" t="s">
-        <v>636</v>
+        <v>605</v>
       </c>
       <c r="E407" t="s">
         <v>4</v>
@@ -13738,7 +13708,7 @@
         <v>4</v>
       </c>
       <c r="I407" t="s">
-        <v>618</v>
+        <v>587</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.3">
@@ -13746,10 +13716,10 @@
         <v>292</v>
       </c>
       <c r="C408" t="s">
-        <v>769</v>
+        <v>728</v>
       </c>
       <c r="D408" t="s">
-        <v>768</v>
+        <v>727</v>
       </c>
       <c r="E408" t="s">
         <v>4</v>
@@ -13764,7 +13734,7 @@
         <v>4</v>
       </c>
       <c r="I408" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.3">
@@ -13789,10 +13759,10 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>1151</v>
+        <v>1100</v>
       </c>
       <c r="D410" t="s">
-        <v>1150</v>
+        <v>1099</v>
       </c>
       <c r="E410" t="s">
         <v>4</v>
@@ -13812,7 +13782,7 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>981</v>
+        <v>931</v>
       </c>
       <c r="E411" t="s">
         <v>4</v>
@@ -13832,13 +13802,13 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>872</v>
+        <v>822</v>
       </c>
       <c r="C412" t="s">
-        <v>1097</v>
+        <v>1046</v>
       </c>
       <c r="D412" t="s">
-        <v>1096</v>
+        <v>1045</v>
       </c>
       <c r="E412" t="s">
         <v>4</v>
@@ -13853,7 +13823,7 @@
         <v>4</v>
       </c>
       <c r="I412" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.3">
@@ -13861,10 +13831,10 @@
         <v>297</v>
       </c>
       <c r="C413" t="s">
-        <v>637</v>
+        <v>606</v>
       </c>
       <c r="D413" t="s">
-        <v>770</v>
+        <v>729</v>
       </c>
       <c r="E413" t="s">
         <v>4</v>
@@ -13879,12 +13849,12 @@
         <v>5</v>
       </c>
       <c r="I413" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>983</v>
+        <v>933</v>
       </c>
       <c r="E414" t="s">
         <v>4</v>
@@ -13904,10 +13874,10 @@
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>982</v>
+        <v>932</v>
       </c>
       <c r="D415" t="s">
-        <v>1152</v>
+        <v>1101</v>
       </c>
       <c r="E415" t="s">
         <v>4</v>
@@ -13930,7 +13900,7 @@
         <v>298</v>
       </c>
       <c r="D416" t="s">
-        <v>699</v>
+        <v>665</v>
       </c>
       <c r="E416" t="s">
         <v>4</v>
@@ -13945,12 +13915,12 @@
         <v>5</v>
       </c>
       <c r="I416" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>984</v>
+        <v>934</v>
       </c>
       <c r="E417" t="s">
         <v>4</v>
@@ -13970,13 +13940,13 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>873</v>
+        <v>823</v>
       </c>
       <c r="C418" t="s">
-        <v>1098</v>
+        <v>1047</v>
       </c>
       <c r="D418" t="s">
-        <v>1099</v>
+        <v>1048</v>
       </c>
       <c r="E418" t="s">
         <v>4</v>
@@ -13991,7 +13961,7 @@
         <v>4</v>
       </c>
       <c r="I418" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.3">
@@ -13999,7 +13969,7 @@
         <v>299</v>
       </c>
       <c r="D419" t="s">
-        <v>700</v>
+        <v>666</v>
       </c>
       <c r="E419" t="s">
         <v>4</v>
@@ -14059,13 +14029,13 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>874</v>
+        <v>824</v>
       </c>
       <c r="C422" t="s">
-        <v>1100</v>
+        <v>1049</v>
       </c>
       <c r="D422" t="s">
-        <v>1101</v>
+        <v>1050</v>
       </c>
       <c r="E422" t="s">
         <v>4</v>
@@ -14080,18 +14050,18 @@
         <v>4</v>
       </c>
       <c r="I422" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>875</v>
+        <v>825</v>
       </c>
       <c r="B423" t="s">
-        <v>1102</v>
+        <v>1051</v>
       </c>
       <c r="C423" t="s">
-        <v>1102</v>
+        <v>1051</v>
       </c>
       <c r="E423" t="s">
         <v>4</v>
@@ -14106,7 +14076,7 @@
         <v>5</v>
       </c>
       <c r="I423" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.3">
@@ -14126,12 +14096,12 @@
         <v>4</v>
       </c>
       <c r="I424" t="s">
-        <v>859</v>
+        <v>809</v>
       </c>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>848</v>
+        <v>798</v>
       </c>
       <c r="E425" t="s">
         <v>4</v>
@@ -14154,7 +14124,7 @@
         <v>303</v>
       </c>
       <c r="D426" t="s">
-        <v>701</v>
+        <v>667</v>
       </c>
       <c r="E426" t="s">
         <v>5</v>
@@ -14169,7 +14139,7 @@
         <v>5</v>
       </c>
       <c r="I426" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.3">
@@ -14194,13 +14164,13 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>876</v>
+        <v>826</v>
       </c>
       <c r="C428" t="s">
-        <v>1103</v>
+        <v>1052</v>
       </c>
       <c r="D428" t="s">
-        <v>1104</v>
+        <v>1053</v>
       </c>
       <c r="E428" t="s">
         <v>4</v>
@@ -14215,12 +14185,12 @@
         <v>4</v>
       </c>
       <c r="I428" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>985</v>
+        <v>935</v>
       </c>
       <c r="E429" t="s">
         <v>4</v>
@@ -14240,7 +14210,7 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>986</v>
+        <v>936</v>
       </c>
       <c r="E430" t="s">
         <v>4</v>
@@ -14260,7 +14230,7 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>987</v>
+        <v>937</v>
       </c>
       <c r="E431" t="s">
         <v>4</v>
@@ -14280,7 +14250,7 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>837</v>
+        <v>787</v>
       </c>
       <c r="E432" t="s">
         <v>5</v>
@@ -14295,7 +14265,7 @@
         <v>5</v>
       </c>
       <c r="I432" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.3">
@@ -14303,7 +14273,7 @@
         <v>305</v>
       </c>
       <c r="D433" t="s">
-        <v>771</v>
+        <v>1171</v>
       </c>
       <c r="E433" t="s">
         <v>5</v>
@@ -14318,15 +14288,15 @@
         <v>5</v>
       </c>
       <c r="I433" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>988</v>
+        <v>938</v>
       </c>
       <c r="D434" t="s">
-        <v>1153</v>
+        <v>1102</v>
       </c>
       <c r="E434" t="s">
         <v>4</v>
@@ -14366,7 +14336,7 @@
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>989</v>
+        <v>939</v>
       </c>
       <c r="E436" t="s">
         <v>4</v>
@@ -14386,7 +14356,7 @@
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>849</v>
+        <v>799</v>
       </c>
       <c r="E437" t="s">
         <v>4</v>
@@ -14406,10 +14376,10 @@
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>838</v>
+        <v>788</v>
       </c>
       <c r="D438" t="s">
-        <v>1105</v>
+        <v>1054</v>
       </c>
       <c r="E438" t="s">
         <v>5</v>
@@ -14432,13 +14402,13 @@
         <v>307</v>
       </c>
       <c r="B439" t="s">
-        <v>638</v>
+        <v>607</v>
       </c>
       <c r="C439" t="s">
-        <v>639</v>
+        <v>608</v>
       </c>
       <c r="D439" t="s">
-        <v>772</v>
+        <v>730</v>
       </c>
       <c r="E439" t="s">
         <v>4</v>
@@ -14458,7 +14428,7 @@
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>990</v>
+        <v>940</v>
       </c>
       <c r="E440" t="s">
         <v>4</v>
@@ -14504,7 +14474,7 @@
         <v>309</v>
       </c>
       <c r="D442" t="s">
-        <v>773</v>
+        <v>731</v>
       </c>
       <c r="E442" t="s">
         <v>4</v>
@@ -14519,15 +14489,15 @@
         <v>5</v>
       </c>
       <c r="I442" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>877</v>
+        <v>827</v>
       </c>
       <c r="D443" t="s">
-        <v>1106</v>
+        <v>1055</v>
       </c>
       <c r="E443" t="s">
         <v>4</v>
@@ -14542,12 +14512,12 @@
         <v>4</v>
       </c>
       <c r="I443" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>991</v>
+        <v>941</v>
       </c>
       <c r="E444" t="s">
         <v>4</v>
@@ -14567,7 +14537,7 @@
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>992</v>
+        <v>942</v>
       </c>
       <c r="E445" t="s">
         <v>4</v>
@@ -14590,13 +14560,13 @@
         <v>310</v>
       </c>
       <c r="B446" t="s">
-        <v>640</v>
+        <v>609</v>
       </c>
       <c r="C446" t="s">
-        <v>640</v>
+        <v>609</v>
       </c>
       <c r="D446" t="s">
-        <v>702</v>
+        <v>668</v>
       </c>
       <c r="E446" t="s">
         <v>4</v>
@@ -14619,10 +14589,7 @@
         <v>311</v>
       </c>
       <c r="C447" t="s">
-        <v>774</v>
-      </c>
-      <c r="D447" t="s">
-        <v>775</v>
+        <v>732</v>
       </c>
       <c r="E447" t="s">
         <v>4</v>
@@ -14642,7 +14609,7 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>993</v>
+        <v>943</v>
       </c>
       <c r="E448" t="s">
         <v>4</v>
@@ -14705,7 +14672,7 @@
         <v>314</v>
       </c>
       <c r="D451" t="s">
-        <v>776</v>
+        <v>733</v>
       </c>
       <c r="E451" t="s">
         <v>4</v>
@@ -14720,12 +14687,12 @@
         <v>4</v>
       </c>
       <c r="I451" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>839</v>
+        <v>789</v>
       </c>
       <c r="E452" t="s">
         <v>5</v>
@@ -14751,7 +14718,7 @@
         <v>315</v>
       </c>
       <c r="D453" t="s">
-        <v>703</v>
+        <v>1172</v>
       </c>
       <c r="E453" t="s">
         <v>4</v>
@@ -14766,7 +14733,7 @@
         <v>4</v>
       </c>
       <c r="I453" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.3">
@@ -14774,13 +14741,13 @@
         <v>316</v>
       </c>
       <c r="B454" t="s">
-        <v>777</v>
+        <v>734</v>
       </c>
       <c r="C454" t="s">
-        <v>641</v>
+        <v>610</v>
       </c>
       <c r="D454" t="s">
-        <v>704</v>
+        <v>669</v>
       </c>
       <c r="E454" t="s">
         <v>4</v>
@@ -14803,10 +14770,10 @@
         <v>317</v>
       </c>
       <c r="C455" t="s">
-        <v>642</v>
+        <v>611</v>
       </c>
       <c r="D455" t="s">
-        <v>778</v>
+        <v>735</v>
       </c>
       <c r="E455" t="s">
         <v>4</v>
@@ -14821,12 +14788,12 @@
         <v>4</v>
       </c>
       <c r="I455" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>994</v>
+        <v>944</v>
       </c>
       <c r="E456" t="s">
         <v>4</v>
@@ -14861,7 +14828,7 @@
         <v>5</v>
       </c>
       <c r="I457" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="458" spans="1:9" x14ac:dyDescent="0.3">
@@ -14906,10 +14873,10 @@
     </row>
     <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>878</v>
+        <v>828</v>
       </c>
       <c r="D460" t="s">
-        <v>1107</v>
+        <v>1056</v>
       </c>
       <c r="E460" t="s">
         <v>4</v>
@@ -14924,7 +14891,7 @@
         <v>4</v>
       </c>
       <c r="I460" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="461" spans="1:9" x14ac:dyDescent="0.3">
@@ -14935,7 +14902,7 @@
         <v>174</v>
       </c>
       <c r="D461" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
       <c r="E461" t="s">
         <v>5</v>
@@ -14955,7 +14922,7 @@
     </row>
     <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>995</v>
+        <v>945</v>
       </c>
       <c r="E462" t="s">
         <v>4</v>
@@ -14978,13 +14945,13 @@
         <v>322</v>
       </c>
       <c r="B463" t="s">
-        <v>779</v>
+        <v>736</v>
       </c>
       <c r="C463" t="s">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="D463" t="s">
-        <v>706</v>
+        <v>671</v>
       </c>
       <c r="E463" t="s">
         <v>4</v>
@@ -14999,15 +14966,15 @@
         <v>5</v>
       </c>
       <c r="I463" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>879</v>
+        <v>829</v>
       </c>
       <c r="D464" t="s">
-        <v>1108</v>
+        <v>1057</v>
       </c>
       <c r="E464" t="s">
         <v>4</v>
@@ -15022,12 +14989,12 @@
         <v>4</v>
       </c>
       <c r="I464" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>996</v>
+        <v>946</v>
       </c>
       <c r="E465" t="s">
         <v>4</v>
@@ -15050,7 +15017,7 @@
         <v>323</v>
       </c>
       <c r="D466" t="s">
-        <v>707</v>
+        <v>672</v>
       </c>
       <c r="E466" t="s">
         <v>4</v>
@@ -15065,7 +15032,7 @@
         <v>5</v>
       </c>
       <c r="I466" t="s">
-        <v>964</v>
+        <v>914</v>
       </c>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.3">
@@ -15073,7 +15040,7 @@
         <v>325</v>
       </c>
       <c r="D467" t="s">
-        <v>781</v>
+        <v>738</v>
       </c>
       <c r="E467" t="s">
         <v>4</v>
@@ -15088,7 +15055,7 @@
         <v>5</v>
       </c>
       <c r="I467" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="468" spans="1:9" x14ac:dyDescent="0.3">
@@ -15096,10 +15063,10 @@
         <v>324</v>
       </c>
       <c r="C468" t="s">
-        <v>780</v>
+        <v>737</v>
       </c>
       <c r="D468" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
       <c r="E468" t="s">
         <v>4</v>
@@ -15114,7 +15081,7 @@
         <v>5</v>
       </c>
       <c r="I468" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.3">
@@ -15139,7 +15106,7 @@
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>997</v>
+        <v>947</v>
       </c>
       <c r="E470" t="s">
         <v>4</v>
@@ -15164,9 +15131,6 @@
       <c r="C471" t="s">
         <v>327</v>
       </c>
-      <c r="D471" t="s">
-        <v>782</v>
-      </c>
       <c r="E471" t="s">
         <v>4</v>
       </c>
@@ -15180,7 +15144,7 @@
         <v>4</v>
       </c>
       <c r="I471" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="472" spans="1:9" x14ac:dyDescent="0.3">
@@ -15188,7 +15152,7 @@
         <v>328</v>
       </c>
       <c r="D472" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
       <c r="E472" t="s">
         <v>5</v>
@@ -15203,7 +15167,7 @@
         <v>5</v>
       </c>
       <c r="I472" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.3">
@@ -15211,10 +15175,10 @@
         <v>329</v>
       </c>
       <c r="C473" t="s">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="D473" t="s">
-        <v>783</v>
+        <v>739</v>
       </c>
       <c r="E473" t="s">
         <v>4</v>
@@ -15229,7 +15193,7 @@
         <v>4</v>
       </c>
       <c r="I473" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.3">
@@ -15237,7 +15201,7 @@
         <v>330</v>
       </c>
       <c r="D474" t="s">
-        <v>710</v>
+        <v>675</v>
       </c>
       <c r="E474" t="s">
         <v>5</v>
@@ -15252,12 +15216,12 @@
         <v>5</v>
       </c>
       <c r="I474" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>998</v>
+        <v>948</v>
       </c>
       <c r="E475" t="s">
         <v>4</v>
@@ -15280,13 +15244,13 @@
         <v>331</v>
       </c>
       <c r="B476" t="s">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="C476" t="s">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="D476" t="s">
-        <v>711</v>
+        <v>676</v>
       </c>
       <c r="E476" t="s">
         <v>5</v>
@@ -15306,10 +15270,10 @@
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>999</v>
+        <v>949</v>
       </c>
       <c r="D477" t="s">
-        <v>1154</v>
+        <v>1103</v>
       </c>
       <c r="E477" t="s">
         <v>4</v>
@@ -15329,7 +15293,7 @@
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="E478" t="s">
         <v>4</v>
@@ -15349,7 +15313,7 @@
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>1001</v>
+        <v>951</v>
       </c>
       <c r="E479" t="s">
         <v>4</v>
@@ -15372,10 +15336,10 @@
         <v>332</v>
       </c>
       <c r="C480" t="s">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="D480" t="s">
-        <v>784</v>
+        <v>740</v>
       </c>
       <c r="E480" t="s">
         <v>4</v>
@@ -15390,21 +15354,21 @@
         <v>5</v>
       </c>
       <c r="I480" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>1002</v>
+        <v>952</v>
       </c>
       <c r="B481" t="s">
-        <v>1155</v>
+        <v>1104</v>
       </c>
       <c r="C481" t="s">
-        <v>1156</v>
+        <v>1105</v>
       </c>
       <c r="D481" t="s">
-        <v>1157</v>
+        <v>1106</v>
       </c>
       <c r="E481" t="s">
         <v>4</v>
@@ -15427,7 +15391,7 @@
         <v>333</v>
       </c>
       <c r="D482" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
       <c r="E482" t="s">
         <v>4</v>
@@ -15450,7 +15414,7 @@
         <v>334</v>
       </c>
       <c r="D483" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
       <c r="E483" t="s">
         <v>4</v>
@@ -15465,18 +15429,18 @@
         <v>5</v>
       </c>
       <c r="I483" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>880</v>
+        <v>830</v>
       </c>
       <c r="C484" t="s">
-        <v>1109</v>
+        <v>1058</v>
       </c>
       <c r="D484" t="s">
-        <v>1110</v>
+        <v>1059</v>
       </c>
       <c r="E484" t="s">
         <v>4</v>
@@ -15491,7 +15455,7 @@
         <v>4</v>
       </c>
       <c r="I484" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="485" spans="1:9" x14ac:dyDescent="0.3">
@@ -15499,10 +15463,10 @@
         <v>335</v>
       </c>
       <c r="C485" t="s">
-        <v>646</v>
+        <v>615</v>
       </c>
       <c r="D485" t="s">
-        <v>785</v>
+        <v>741</v>
       </c>
       <c r="E485" t="s">
         <v>4</v>
@@ -15517,12 +15481,12 @@
         <v>4</v>
       </c>
       <c r="I485" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>1003</v>
+        <v>953</v>
       </c>
       <c r="E486" t="s">
         <v>4</v>
@@ -15562,16 +15526,16 @@
     </row>
     <row r="488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>1004</v>
+        <v>954</v>
       </c>
       <c r="B488" t="s">
-        <v>1158</v>
+        <v>1107</v>
       </c>
       <c r="C488" t="s">
-        <v>1158</v>
+        <v>1107</v>
       </c>
       <c r="D488" t="s">
-        <v>1159</v>
+        <v>1108</v>
       </c>
       <c r="E488" t="s">
         <v>4</v>
@@ -15594,7 +15558,7 @@
         <v>337</v>
       </c>
       <c r="D489" t="s">
-        <v>786</v>
+        <v>742</v>
       </c>
       <c r="E489" t="s">
         <v>4</v>
@@ -15609,12 +15573,12 @@
         <v>4</v>
       </c>
       <c r="I489" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="E490" t="s">
         <v>5</v>
@@ -15636,9 +15600,6 @@
       <c r="A491" t="s">
         <v>338</v>
       </c>
-      <c r="D491" t="s">
-        <v>787</v>
-      </c>
       <c r="E491" t="s">
         <v>4</v>
       </c>
@@ -15657,7 +15618,7 @@
     </row>
     <row r="492" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>1005</v>
+        <v>955</v>
       </c>
       <c r="E492" t="s">
         <v>4</v>
@@ -15677,10 +15638,10 @@
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>1006</v>
+        <v>956</v>
       </c>
       <c r="D493" t="s">
-        <v>1160</v>
+        <v>1109</v>
       </c>
       <c r="E493" t="s">
         <v>4</v>
@@ -15700,7 +15661,7 @@
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>1007</v>
+        <v>957</v>
       </c>
       <c r="E494" t="s">
         <v>4</v>
@@ -15720,16 +15681,16 @@
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>1008</v>
+        <v>958</v>
       </c>
       <c r="B495" t="s">
-        <v>1161</v>
+        <v>1110</v>
       </c>
       <c r="C495" t="s">
-        <v>1162</v>
+        <v>1111</v>
       </c>
       <c r="D495" t="s">
-        <v>1163</v>
+        <v>1112</v>
       </c>
       <c r="E495" t="s">
         <v>4</v>
@@ -15752,7 +15713,7 @@
         <v>339</v>
       </c>
       <c r="D496" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
       <c r="E496" t="s">
         <v>5</v>
@@ -15767,7 +15728,7 @@
         <v>5</v>
       </c>
       <c r="I496" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.3">
@@ -15775,13 +15736,10 @@
         <v>438</v>
       </c>
       <c r="B497" t="s">
-        <v>780</v>
+        <v>737</v>
       </c>
       <c r="C497" t="s">
-        <v>780</v>
-      </c>
-      <c r="D497" t="s">
-        <v>715</v>
+        <v>737</v>
       </c>
       <c r="E497" t="s">
         <v>4</v>
@@ -15807,7 +15765,7 @@
         <v>439</v>
       </c>
       <c r="D498" t="s">
-        <v>788</v>
+        <v>743</v>
       </c>
       <c r="E498" t="s">
         <v>4</v>
@@ -15822,7 +15780,7 @@
         <v>5</v>
       </c>
       <c r="I498" t="s">
-        <v>964</v>
+        <v>914</v>
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.3">
@@ -15847,7 +15805,7 @@
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>1009</v>
+        <v>959</v>
       </c>
       <c r="E500" t="s">
         <v>4</v>
@@ -15867,13 +15825,13 @@
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>1010</v>
+        <v>960</v>
       </c>
       <c r="C501" t="s">
-        <v>1164</v>
+        <v>1113</v>
       </c>
       <c r="D501" t="s">
-        <v>1165</v>
+        <v>1114</v>
       </c>
       <c r="E501" t="s">
         <v>4</v>
@@ -15896,10 +15854,10 @@
         <v>341</v>
       </c>
       <c r="C502" t="s">
-        <v>647</v>
+        <v>616</v>
       </c>
       <c r="D502" t="s">
-        <v>716</v>
+        <v>680</v>
       </c>
       <c r="E502" t="s">
         <v>4</v>
@@ -15914,7 +15872,7 @@
         <v>4</v>
       </c>
       <c r="I502" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.3">
@@ -15922,7 +15880,7 @@
         <v>342</v>
       </c>
       <c r="D503" t="s">
-        <v>717</v>
+        <v>681</v>
       </c>
       <c r="E503" t="s">
         <v>4</v>
@@ -15937,12 +15895,12 @@
         <v>4</v>
       </c>
       <c r="I503" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>1011</v>
+        <v>961</v>
       </c>
       <c r="E504" t="s">
         <v>4</v>
@@ -15965,7 +15923,7 @@
         <v>343</v>
       </c>
       <c r="D505" t="s">
-        <v>789</v>
+        <v>744</v>
       </c>
       <c r="E505" t="s">
         <v>4</v>
@@ -15980,12 +15938,12 @@
         <v>4</v>
       </c>
       <c r="I505" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>1012</v>
+        <v>962</v>
       </c>
       <c r="E506" t="s">
         <v>4</v>
@@ -16008,10 +15966,10 @@
         <v>344</v>
       </c>
       <c r="C507" t="s">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="D507" t="s">
-        <v>790</v>
+        <v>745</v>
       </c>
       <c r="E507" t="s">
         <v>4</v>
@@ -16026,7 +15984,7 @@
         <v>4</v>
       </c>
       <c r="I507" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.3">
@@ -16034,13 +15992,13 @@
         <v>345</v>
       </c>
       <c r="B508" t="s">
-        <v>638</v>
+        <v>607</v>
       </c>
       <c r="C508" t="s">
-        <v>639</v>
+        <v>608</v>
       </c>
       <c r="D508" t="s">
-        <v>718</v>
+        <v>682</v>
       </c>
       <c r="E508" t="s">
         <v>4</v>
@@ -16060,10 +16018,10 @@
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>881</v>
+        <v>831</v>
       </c>
       <c r="D509" t="s">
-        <v>1111</v>
+        <v>1060</v>
       </c>
       <c r="E509" t="s">
         <v>4</v>
@@ -16078,15 +16036,15 @@
         <v>4</v>
       </c>
       <c r="I509" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>1013</v>
+        <v>963</v>
       </c>
       <c r="D510" t="s">
-        <v>1167</v>
+        <v>1116</v>
       </c>
       <c r="E510" t="s">
         <v>4</v>
@@ -16109,10 +16067,10 @@
         <v>346</v>
       </c>
       <c r="C511" t="s">
-        <v>649</v>
+        <v>618</v>
       </c>
       <c r="D511" t="s">
-        <v>791</v>
+        <v>746</v>
       </c>
       <c r="E511" t="s">
         <v>4</v>
@@ -16127,12 +16085,12 @@
         <v>5</v>
       </c>
       <c r="I511" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>1014</v>
+        <v>964</v>
       </c>
       <c r="E512" t="s">
         <v>4</v>
@@ -16155,7 +16113,7 @@
         <v>347</v>
       </c>
       <c r="D513" t="s">
-        <v>719</v>
+        <v>1173</v>
       </c>
       <c r="E513" t="s">
         <v>4</v>
@@ -16170,7 +16128,7 @@
         <v>4</v>
       </c>
       <c r="I513" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.3">
@@ -16190,7 +16148,7 @@
         <v>5</v>
       </c>
       <c r="I514" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.3">
@@ -16198,7 +16156,7 @@
         <v>349</v>
       </c>
       <c r="D515" t="s">
-        <v>720</v>
+        <v>683</v>
       </c>
       <c r="E515" t="s">
         <v>4</v>
@@ -16213,15 +16171,15 @@
         <v>5</v>
       </c>
       <c r="I515" t="s">
-        <v>964</v>
+        <v>914</v>
       </c>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>1015</v>
+        <v>965</v>
       </c>
       <c r="D516" t="s">
-        <v>1168</v>
+        <v>1117</v>
       </c>
       <c r="E516" t="s">
         <v>4</v>
@@ -16244,10 +16202,10 @@
         <v>350</v>
       </c>
       <c r="C517" t="s">
-        <v>650</v>
+        <v>619</v>
       </c>
       <c r="D517" t="s">
-        <v>721</v>
+        <v>684</v>
       </c>
       <c r="E517" t="s">
         <v>4</v>
@@ -16262,7 +16220,7 @@
         <v>4</v>
       </c>
       <c r="I517" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="518" spans="1:9" x14ac:dyDescent="0.3">
@@ -16287,7 +16245,7 @@
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>1016</v>
+        <v>966</v>
       </c>
       <c r="E519" t="s">
         <v>4</v>
@@ -16307,7 +16265,7 @@
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>1017</v>
+        <v>967</v>
       </c>
       <c r="E520" t="s">
         <v>4</v>
@@ -16330,7 +16288,7 @@
         <v>353</v>
       </c>
       <c r="D521" t="s">
-        <v>722</v>
+        <v>685</v>
       </c>
       <c r="E521" t="s">
         <v>4</v>
@@ -16345,12 +16303,12 @@
         <v>4</v>
       </c>
       <c r="I521" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
-        <v>1018</v>
+        <v>968</v>
       </c>
       <c r="E522" t="s">
         <v>4</v>
@@ -16373,7 +16331,7 @@
         <v>352</v>
       </c>
       <c r="D523" t="s">
-        <v>792</v>
+        <v>747</v>
       </c>
       <c r="E523" t="s">
         <v>4</v>
@@ -16388,12 +16346,12 @@
         <v>4</v>
       </c>
       <c r="I523" t="s">
-        <v>862</v>
+        <v>812</v>
       </c>
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>1019</v>
+        <v>969</v>
       </c>
       <c r="E524" t="s">
         <v>4</v>
@@ -16413,7 +16371,7 @@
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>1020</v>
+        <v>970</v>
       </c>
       <c r="E525" t="s">
         <v>4</v>
@@ -16456,13 +16414,13 @@
         <v>355</v>
       </c>
       <c r="B527" t="s">
-        <v>793</v>
+        <v>748</v>
       </c>
       <c r="C527" t="s">
-        <v>793</v>
+        <v>748</v>
       </c>
       <c r="D527" t="s">
-        <v>794</v>
+        <v>749</v>
       </c>
       <c r="E527" t="s">
         <v>4</v>
@@ -16485,7 +16443,7 @@
         <v>356</v>
       </c>
       <c r="D528" t="s">
-        <v>795</v>
+        <v>750</v>
       </c>
       <c r="E528" t="s">
         <v>4</v>
@@ -16500,7 +16458,7 @@
         <v>4</v>
       </c>
       <c r="I528" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.3">
@@ -16508,7 +16466,7 @@
         <v>357</v>
       </c>
       <c r="D529" t="s">
-        <v>723</v>
+        <v>686</v>
       </c>
       <c r="E529" t="s">
         <v>4</v>
@@ -16531,10 +16489,10 @@
         <v>358</v>
       </c>
       <c r="C530" t="s">
-        <v>651</v>
+        <v>620</v>
       </c>
       <c r="D530" t="s">
-        <v>724</v>
+        <v>687</v>
       </c>
       <c r="E530" t="s">
         <v>4</v>
@@ -16549,7 +16507,7 @@
         <v>4</v>
       </c>
       <c r="I530" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.3">
@@ -16574,7 +16532,7 @@
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>851</v>
+        <v>801</v>
       </c>
       <c r="E532" t="s">
         <v>4</v>
@@ -16634,7 +16592,7 @@
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>1021</v>
+        <v>971</v>
       </c>
       <c r="E535" t="s">
         <v>4</v>
@@ -16657,7 +16615,7 @@
         <v>362</v>
       </c>
       <c r="D536" t="s">
-        <v>725</v>
+        <v>688</v>
       </c>
       <c r="E536" t="s">
         <v>5</v>
@@ -16672,7 +16630,7 @@
         <v>5</v>
       </c>
       <c r="I536" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.3">
@@ -16680,7 +16638,7 @@
         <v>363</v>
       </c>
       <c r="D537" t="s">
-        <v>796</v>
+        <v>751</v>
       </c>
       <c r="E537" t="s">
         <v>4</v>
@@ -16695,12 +16653,12 @@
         <v>5</v>
       </c>
       <c r="I537" t="s">
-        <v>964</v>
+        <v>914</v>
       </c>
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>1022</v>
+        <v>972</v>
       </c>
       <c r="E538" t="s">
         <v>4</v>
@@ -16720,7 +16678,7 @@
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>1023</v>
+        <v>973</v>
       </c>
       <c r="E539" t="s">
         <v>4</v>
@@ -16783,7 +16741,7 @@
         <v>366</v>
       </c>
       <c r="D542" t="s">
-        <v>726</v>
+        <v>1174</v>
       </c>
       <c r="E542" t="s">
         <v>5</v>
@@ -16798,7 +16756,7 @@
         <v>5</v>
       </c>
       <c r="I542" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.3">
@@ -16809,7 +16767,7 @@
         <v>367</v>
       </c>
       <c r="D543" t="s">
-        <v>826</v>
+        <v>776</v>
       </c>
       <c r="E543" t="s">
         <v>4</v>
@@ -16824,7 +16782,7 @@
         <v>5</v>
       </c>
       <c r="I543" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.3">
@@ -16832,7 +16790,7 @@
         <v>368</v>
       </c>
       <c r="D544" t="s">
-        <v>1070</v>
+        <v>1020</v>
       </c>
       <c r="E544" t="s">
         <v>4</v>
@@ -16847,7 +16805,7 @@
         <v>5</v>
       </c>
       <c r="I544" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.3">
@@ -16855,10 +16813,10 @@
         <v>369</v>
       </c>
       <c r="C545" t="s">
-        <v>652</v>
+        <v>621</v>
       </c>
       <c r="D545" t="s">
-        <v>727</v>
+        <v>689</v>
       </c>
       <c r="E545" t="s">
         <v>4</v>
@@ -16881,7 +16839,7 @@
         <v>370</v>
       </c>
       <c r="D546" t="s">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="E546" t="s">
         <v>4</v>
@@ -16896,18 +16854,18 @@
         <v>4</v>
       </c>
       <c r="I546" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>852</v>
+        <v>802</v>
       </c>
       <c r="B547" t="s">
-        <v>1112</v>
+        <v>1061</v>
       </c>
       <c r="C547" t="s">
-        <v>1112</v>
+        <v>1061</v>
       </c>
       <c r="E547" t="s">
         <v>4</v>
@@ -16930,10 +16888,10 @@
         <v>371</v>
       </c>
       <c r="C548" t="s">
-        <v>653</v>
+        <v>622</v>
       </c>
       <c r="D548" t="s">
-        <v>1069</v>
+        <v>1019</v>
       </c>
       <c r="E548" t="s">
         <v>4</v>
@@ -16948,7 +16906,7 @@
         <v>4</v>
       </c>
       <c r="I548" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.3">
@@ -16956,13 +16914,13 @@
         <v>372</v>
       </c>
       <c r="B549" t="s">
-        <v>797</v>
+        <v>752</v>
       </c>
       <c r="C549" t="s">
-        <v>797</v>
+        <v>752</v>
       </c>
       <c r="D549" t="s">
-        <v>798</v>
+        <v>1175</v>
       </c>
       <c r="E549" t="s">
         <v>4</v>
@@ -16977,12 +16935,12 @@
         <v>5</v>
       </c>
       <c r="I549" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>1024</v>
+        <v>974</v>
       </c>
       <c r="E550" t="s">
         <v>4</v>
@@ -17017,15 +16975,15 @@
         <v>5</v>
       </c>
       <c r="I551" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="552" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>840</v>
+        <v>790</v>
       </c>
       <c r="D552" t="s">
-        <v>1113</v>
+        <v>1062</v>
       </c>
       <c r="E552" t="s">
         <v>5</v>
@@ -17040,7 +16998,7 @@
         <v>5</v>
       </c>
       <c r="I552" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.3">
@@ -17060,12 +17018,12 @@
         <v>5</v>
       </c>
       <c r="I553" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>853</v>
+        <v>803</v>
       </c>
       <c r="E554" t="s">
         <v>4</v>
@@ -17080,12 +17038,12 @@
         <v>5</v>
       </c>
       <c r="I554" t="s">
-        <v>1068</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>1025</v>
+        <v>975</v>
       </c>
       <c r="E555" t="s">
         <v>4</v>
@@ -17108,7 +17066,7 @@
         <v>375</v>
       </c>
       <c r="D556" t="s">
-        <v>729</v>
+        <v>691</v>
       </c>
       <c r="E556" t="s">
         <v>4</v>
@@ -17123,21 +17081,21 @@
         <v>5</v>
       </c>
       <c r="I556" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>1026</v>
+        <v>976</v>
       </c>
       <c r="B557" t="s">
-        <v>1169</v>
+        <v>1118</v>
       </c>
       <c r="C557" t="s">
-        <v>1169</v>
+        <v>1118</v>
       </c>
       <c r="D557" t="s">
-        <v>1170</v>
+        <v>1119</v>
       </c>
       <c r="E557" t="s">
         <v>4</v>
@@ -17160,7 +17118,7 @@
         <v>378</v>
       </c>
       <c r="D558" t="s">
-        <v>799</v>
+        <v>753</v>
       </c>
       <c r="E558" t="s">
         <v>4</v>
@@ -17195,15 +17153,15 @@
         <v>5</v>
       </c>
       <c r="I559" t="s">
-        <v>894</v>
+        <v>844</v>
       </c>
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>882</v>
+        <v>832</v>
       </c>
       <c r="D560" t="s">
-        <v>1114</v>
+        <v>1063</v>
       </c>
       <c r="E560" t="s">
         <v>4</v>
@@ -17218,7 +17176,7 @@
         <v>4</v>
       </c>
       <c r="I560" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.3">
@@ -17243,7 +17201,7 @@
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>1027</v>
+        <v>977</v>
       </c>
       <c r="E562" t="s">
         <v>4</v>
@@ -17266,13 +17224,13 @@
         <v>379</v>
       </c>
       <c r="B563" t="s">
-        <v>654</v>
+        <v>623</v>
       </c>
       <c r="C563" t="s">
-        <v>655</v>
+        <v>624</v>
       </c>
       <c r="D563" t="s">
-        <v>730</v>
+        <v>1176</v>
       </c>
       <c r="E563" t="s">
         <v>4</v>
@@ -17292,10 +17250,10 @@
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>883</v>
+        <v>833</v>
       </c>
       <c r="D564" t="s">
-        <v>1115</v>
+        <v>1064</v>
       </c>
       <c r="E564" t="s">
         <v>4</v>
@@ -17310,12 +17268,12 @@
         <v>5</v>
       </c>
       <c r="I564" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>1028</v>
+        <v>978</v>
       </c>
       <c r="E565" t="s">
         <v>4</v>
@@ -17335,10 +17293,10 @@
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>1029</v>
+        <v>979</v>
       </c>
       <c r="D566" t="s">
-        <v>1171</v>
+        <v>1120</v>
       </c>
       <c r="E566" t="s">
         <v>4</v>
@@ -17358,7 +17316,7 @@
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>1030</v>
+        <v>980</v>
       </c>
       <c r="E567" t="s">
         <v>4</v>
@@ -17378,16 +17336,16 @@
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>1031</v>
+        <v>981</v>
       </c>
       <c r="B568" t="s">
-        <v>1172</v>
+        <v>1121</v>
       </c>
       <c r="C568" t="s">
-        <v>1174</v>
+        <v>1123</v>
       </c>
       <c r="D568" t="s">
-        <v>1173</v>
+        <v>1122</v>
       </c>
       <c r="E568" t="s">
         <v>4</v>
@@ -17407,13 +17365,13 @@
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>1032</v>
+        <v>982</v>
       </c>
       <c r="B569" t="s">
-        <v>1175</v>
+        <v>1124</v>
       </c>
       <c r="C569" t="s">
-        <v>1176</v>
+        <v>1125</v>
       </c>
       <c r="E569" t="s">
         <v>4</v>
@@ -17433,7 +17391,7 @@
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>1033</v>
+        <v>983</v>
       </c>
       <c r="E570" t="s">
         <v>4</v>
@@ -17456,7 +17414,7 @@
         <v>380</v>
       </c>
       <c r="D571" t="s">
-        <v>731</v>
+        <v>692</v>
       </c>
       <c r="E571" t="s">
         <v>5</v>
@@ -17476,7 +17434,7 @@
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>1034</v>
+        <v>984</v>
       </c>
       <c r="E572" t="s">
         <v>4</v>
@@ -17496,7 +17454,7 @@
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>1035</v>
+        <v>985</v>
       </c>
       <c r="E573" t="s">
         <v>4</v>
@@ -17516,7 +17474,7 @@
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>1036</v>
+        <v>986</v>
       </c>
       <c r="E574" t="s">
         <v>4</v>
@@ -17536,7 +17494,7 @@
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>1037</v>
+        <v>987</v>
       </c>
       <c r="E575" t="s">
         <v>4</v>
@@ -17559,13 +17517,13 @@
         <v>382</v>
       </c>
       <c r="B576" t="s">
-        <v>657</v>
+        <v>626</v>
       </c>
       <c r="C576" t="s">
-        <v>657</v>
+        <v>626</v>
       </c>
       <c r="D576" t="s">
-        <v>801</v>
+        <v>755</v>
       </c>
       <c r="E576" t="s">
         <v>4</v>
@@ -17580,7 +17538,7 @@
         <v>4</v>
       </c>
       <c r="I576" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.3">
@@ -17588,13 +17546,13 @@
         <v>381</v>
       </c>
       <c r="B577" t="s">
-        <v>656</v>
+        <v>625</v>
       </c>
       <c r="C577" t="s">
-        <v>656</v>
+        <v>625</v>
       </c>
       <c r="D577" t="s">
-        <v>800</v>
+        <v>754</v>
       </c>
       <c r="E577" t="s">
         <v>4</v>
@@ -17609,18 +17567,18 @@
         <v>5</v>
       </c>
       <c r="I577" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>884</v>
+        <v>834</v>
       </c>
       <c r="C578" t="s">
-        <v>1116</v>
+        <v>1065</v>
       </c>
       <c r="D578" t="s">
-        <v>1117</v>
+        <v>1066</v>
       </c>
       <c r="E578" t="s">
         <v>4</v>
@@ -17635,12 +17593,12 @@
         <v>4</v>
       </c>
       <c r="I578" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>1038</v>
+        <v>988</v>
       </c>
       <c r="E579" t="s">
         <v>4</v>
@@ -17660,7 +17618,7 @@
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>1039</v>
+        <v>989</v>
       </c>
       <c r="E580" t="s">
         <v>4</v>
@@ -17695,12 +17653,12 @@
         <v>4</v>
       </c>
       <c r="I581" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>1040</v>
+        <v>990</v>
       </c>
       <c r="E582" t="s">
         <v>4</v>
@@ -17720,7 +17678,7 @@
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>1041</v>
+        <v>991</v>
       </c>
       <c r="E583" t="s">
         <v>4</v>
@@ -17740,7 +17698,7 @@
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>1042</v>
+        <v>992</v>
       </c>
       <c r="E584" t="s">
         <v>4</v>
@@ -17760,13 +17718,13 @@
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>885</v>
+        <v>835</v>
       </c>
       <c r="C585" t="s">
-        <v>1118</v>
+        <v>1067</v>
       </c>
       <c r="D585" t="s">
-        <v>1119</v>
+        <v>1068</v>
       </c>
       <c r="E585" t="s">
         <v>4</v>
@@ -17781,7 +17739,7 @@
         <v>5</v>
       </c>
       <c r="I585" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.3">
@@ -17789,7 +17747,7 @@
         <v>384</v>
       </c>
       <c r="D586" t="s">
-        <v>802</v>
+        <v>1177</v>
       </c>
       <c r="E586" t="s">
         <v>4</v>
@@ -17809,7 +17767,7 @@
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>1043</v>
+        <v>993</v>
       </c>
       <c r="E587" t="s">
         <v>4</v>
@@ -17824,15 +17782,15 @@
         <v>5</v>
       </c>
       <c r="I587" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>886</v>
+        <v>836</v>
       </c>
       <c r="D588" t="s">
-        <v>1120</v>
+        <v>1069</v>
       </c>
       <c r="E588" t="s">
         <v>4</v>
@@ -17847,12 +17805,12 @@
         <v>5</v>
       </c>
       <c r="I588" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>1044</v>
+        <v>994</v>
       </c>
       <c r="E589" t="s">
         <v>4</v>
@@ -17875,13 +17833,13 @@
         <v>385</v>
       </c>
       <c r="B590" t="s">
-        <v>1177</v>
+        <v>1126</v>
       </c>
       <c r="C590" t="s">
-        <v>1177</v>
+        <v>1126</v>
       </c>
       <c r="D590" t="s">
-        <v>803</v>
+        <v>1178</v>
       </c>
       <c r="E590" t="s">
         <v>4</v>
@@ -17896,7 +17854,7 @@
         <v>5</v>
       </c>
       <c r="I590" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.3">
@@ -17904,7 +17862,7 @@
         <v>386</v>
       </c>
       <c r="D591" t="s">
-        <v>732</v>
+        <v>693</v>
       </c>
       <c r="E591" t="s">
         <v>4</v>
@@ -17919,7 +17877,7 @@
         <v>4</v>
       </c>
       <c r="I591" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.3">
@@ -17927,10 +17885,10 @@
         <v>387</v>
       </c>
       <c r="C592" t="s">
-        <v>658</v>
+        <v>627</v>
       </c>
       <c r="D592" t="s">
-        <v>804</v>
+        <v>1179</v>
       </c>
       <c r="E592" t="s">
         <v>4</v>
@@ -17945,12 +17903,12 @@
         <v>4</v>
       </c>
       <c r="I592" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>1045</v>
+        <v>995</v>
       </c>
       <c r="E593" t="s">
         <v>4</v>
@@ -17985,7 +17943,7 @@
         <v>4</v>
       </c>
       <c r="I594" t="s">
-        <v>1180</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.3">
@@ -17993,10 +17951,10 @@
         <v>389</v>
       </c>
       <c r="C595" t="s">
-        <v>659</v>
+        <v>628</v>
       </c>
       <c r="D595" t="s">
-        <v>805</v>
+        <v>1180</v>
       </c>
       <c r="E595" t="s">
         <v>4</v>
@@ -18011,7 +17969,7 @@
         <v>4</v>
       </c>
       <c r="I595" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.3">
@@ -18019,10 +17977,10 @@
         <v>390</v>
       </c>
       <c r="C596" t="s">
-        <v>660</v>
+        <v>629</v>
       </c>
       <c r="D596" t="s">
-        <v>733</v>
+        <v>694</v>
       </c>
       <c r="E596" t="s">
         <v>4</v>
@@ -18037,7 +17995,7 @@
         <v>4</v>
       </c>
       <c r="I596" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.3">
@@ -18057,7 +18015,7 @@
         <v>5</v>
       </c>
       <c r="I597" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.3">
@@ -18065,7 +18023,7 @@
         <v>392</v>
       </c>
       <c r="D598" t="s">
-        <v>734</v>
+        <v>695</v>
       </c>
       <c r="E598" t="s">
         <v>4</v>
@@ -18080,12 +18038,12 @@
         <v>4</v>
       </c>
       <c r="I598" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>1046</v>
+        <v>996</v>
       </c>
       <c r="E599" t="s">
         <v>4</v>
@@ -18108,10 +18066,10 @@
         <v>393</v>
       </c>
       <c r="C600" t="s">
-        <v>661</v>
+        <v>630</v>
       </c>
       <c r="D600" t="s">
-        <v>735</v>
+        <v>696</v>
       </c>
       <c r="E600" t="s">
         <v>4</v>
@@ -18126,12 +18084,12 @@
         <v>4</v>
       </c>
       <c r="I600" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>1047</v>
+        <v>997</v>
       </c>
       <c r="E601" t="s">
         <v>4</v>
@@ -18154,10 +18112,10 @@
         <v>398</v>
       </c>
       <c r="C602" t="s">
-        <v>809</v>
+        <v>759</v>
       </c>
       <c r="D602" t="s">
-        <v>810</v>
+        <v>760</v>
       </c>
       <c r="E602" t="s">
         <v>4</v>
@@ -18177,10 +18135,10 @@
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>1048</v>
+        <v>998</v>
       </c>
       <c r="D603" t="s">
-        <v>1178</v>
+        <v>1127</v>
       </c>
       <c r="E603" t="s">
         <v>4</v>
@@ -18200,7 +18158,7 @@
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>1049</v>
+        <v>999</v>
       </c>
       <c r="E604" t="s">
         <v>4</v>
@@ -18235,7 +18193,7 @@
         <v>5</v>
       </c>
       <c r="I605" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.3">
@@ -18243,7 +18201,7 @@
         <v>395</v>
       </c>
       <c r="D606" t="s">
-        <v>806</v>
+        <v>756</v>
       </c>
       <c r="E606" t="s">
         <v>4</v>
@@ -18258,7 +18216,7 @@
         <v>4</v>
       </c>
       <c r="I606" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.3">
@@ -18269,7 +18227,7 @@
         <v>396</v>
       </c>
       <c r="D607" t="s">
-        <v>807</v>
+        <v>757</v>
       </c>
       <c r="E607" t="s">
         <v>4</v>
@@ -18284,21 +18242,21 @@
         <v>4</v>
       </c>
       <c r="I607" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>887</v>
+        <v>837</v>
       </c>
       <c r="B608" t="s">
-        <v>665</v>
+        <v>634</v>
       </c>
       <c r="C608" t="s">
-        <v>665</v>
+        <v>634</v>
       </c>
       <c r="D608" t="s">
-        <v>1121</v>
+        <v>1070</v>
       </c>
       <c r="E608" t="s">
         <v>4</v>
@@ -18313,12 +18271,12 @@
         <v>4</v>
       </c>
       <c r="I608" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="E609" t="s">
         <v>4</v>
@@ -18341,7 +18299,7 @@
         <v>397</v>
       </c>
       <c r="D610" t="s">
-        <v>808</v>
+        <v>758</v>
       </c>
       <c r="E610" t="s">
         <v>5</v>
@@ -18356,12 +18314,12 @@
         <v>5</v>
       </c>
       <c r="I610" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>1051</v>
+        <v>1001</v>
       </c>
       <c r="E611" t="s">
         <v>4</v>
@@ -18381,7 +18339,7 @@
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>841</v>
+        <v>791</v>
       </c>
       <c r="E612" t="s">
         <v>5</v>
@@ -18401,7 +18359,7 @@
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>1052</v>
+        <v>1002</v>
       </c>
       <c r="E613" t="s">
         <v>4</v>
@@ -18436,12 +18394,12 @@
         <v>4</v>
       </c>
       <c r="I614" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>1053</v>
+        <v>1003</v>
       </c>
       <c r="E615" t="s">
         <v>4</v>
@@ -18516,7 +18474,7 @@
         <v>5</v>
       </c>
       <c r="I618" t="s">
-        <v>1068</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.3">
@@ -18524,13 +18482,13 @@
         <v>401</v>
       </c>
       <c r="B619" t="s">
-        <v>662</v>
+        <v>631</v>
       </c>
       <c r="C619" t="s">
-        <v>662</v>
+        <v>631</v>
       </c>
       <c r="D619" t="s">
-        <v>736</v>
+        <v>697</v>
       </c>
       <c r="E619" t="s">
         <v>4</v>
@@ -18553,10 +18511,10 @@
         <v>403</v>
       </c>
       <c r="C620" t="s">
-        <v>663</v>
+        <v>632</v>
       </c>
       <c r="D620" t="s">
-        <v>811</v>
+        <v>761</v>
       </c>
       <c r="E620" t="s">
         <v>4</v>
@@ -18571,7 +18529,7 @@
         <v>4</v>
       </c>
       <c r="I620" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.3">
@@ -18631,7 +18589,7 @@
         <v>5</v>
       </c>
       <c r="I623" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.3">
@@ -18639,10 +18597,10 @@
         <v>407</v>
       </c>
       <c r="C624" t="s">
-        <v>664</v>
+        <v>633</v>
       </c>
       <c r="D624" t="s">
-        <v>737</v>
+        <v>698</v>
       </c>
       <c r="E624" t="s">
         <v>4</v>
@@ -18657,7 +18615,7 @@
         <v>4</v>
       </c>
       <c r="I624" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.3">
@@ -18677,7 +18635,7 @@
         <v>4</v>
       </c>
       <c r="I625" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.3">
@@ -18685,10 +18643,10 @@
         <v>409</v>
       </c>
       <c r="C626" t="s">
-        <v>665</v>
+        <v>634</v>
       </c>
       <c r="D626" t="s">
-        <v>812</v>
+        <v>762</v>
       </c>
       <c r="E626" t="s">
         <v>4</v>
@@ -18703,7 +18661,7 @@
         <v>5</v>
       </c>
       <c r="I626" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.3">
@@ -18711,13 +18669,13 @@
         <v>410</v>
       </c>
       <c r="B627" t="s">
-        <v>813</v>
+        <v>763</v>
       </c>
       <c r="C627" t="s">
-        <v>813</v>
+        <v>763</v>
       </c>
       <c r="D627" t="s">
-        <v>814</v>
+        <v>764</v>
       </c>
       <c r="E627" t="s">
         <v>4</v>
@@ -18732,7 +18690,7 @@
         <v>5</v>
       </c>
       <c r="I627" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.3">
@@ -18740,10 +18698,10 @@
         <v>411</v>
       </c>
       <c r="C628" t="s">
-        <v>666</v>
+        <v>635</v>
       </c>
       <c r="D628" t="s">
-        <v>815</v>
+        <v>765</v>
       </c>
       <c r="E628" t="s">
         <v>4</v>
@@ -18758,7 +18716,7 @@
         <v>4</v>
       </c>
       <c r="I628" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.3">
@@ -18778,7 +18736,7 @@
         <v>4</v>
       </c>
       <c r="I629" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.3">
@@ -18786,7 +18744,7 @@
         <v>413</v>
       </c>
       <c r="D630" t="s">
-        <v>816</v>
+        <v>766</v>
       </c>
       <c r="E630" t="s">
         <v>4</v>
@@ -18801,12 +18759,12 @@
         <v>4</v>
       </c>
       <c r="I630" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>1054</v>
+        <v>1004</v>
       </c>
       <c r="E631" t="s">
         <v>4</v>
@@ -18829,13 +18787,13 @@
         <v>414</v>
       </c>
       <c r="B632" t="s">
-        <v>667</v>
+        <v>636</v>
       </c>
       <c r="C632" t="s">
-        <v>667</v>
+        <v>636</v>
       </c>
       <c r="D632" t="s">
-        <v>817</v>
+        <v>767</v>
       </c>
       <c r="E632" t="s">
         <v>4</v>
@@ -18858,10 +18816,10 @@
         <v>415</v>
       </c>
       <c r="C633" t="s">
-        <v>818</v>
+        <v>768</v>
       </c>
       <c r="D633" t="s">
-        <v>819</v>
+        <v>769</v>
       </c>
       <c r="E633" t="s">
         <v>4</v>
@@ -18876,7 +18834,7 @@
         <v>4</v>
       </c>
       <c r="I633" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.3">
@@ -18887,7 +18845,7 @@
         <v>416</v>
       </c>
       <c r="D634" t="s">
-        <v>738</v>
+        <v>699</v>
       </c>
       <c r="E634" t="s">
         <v>4</v>
@@ -18902,7 +18860,7 @@
         <v>5</v>
       </c>
       <c r="I634" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.3">
@@ -18922,12 +18880,12 @@
         <v>4</v>
       </c>
       <c r="I635" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>1055</v>
+        <v>1005</v>
       </c>
       <c r="E636" t="s">
         <v>4</v>
@@ -18947,7 +18905,7 @@
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>1056</v>
+        <v>1006</v>
       </c>
       <c r="E637" t="s">
         <v>4</v>
@@ -19002,7 +18960,7 @@
         <v>5</v>
       </c>
       <c r="I639" t="s">
-        <v>854</v>
+        <v>804</v>
       </c>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.3">
@@ -19022,12 +18980,12 @@
         <v>5</v>
       </c>
       <c r="I640" t="s">
-        <v>964</v>
+        <v>914</v>
       </c>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>1057</v>
+        <v>1007</v>
       </c>
       <c r="E641" t="s">
         <v>4</v>
@@ -19050,7 +19008,7 @@
         <v>420</v>
       </c>
       <c r="D642" t="s">
-        <v>820</v>
+        <v>770</v>
       </c>
       <c r="E642" t="s">
         <v>4</v>
@@ -19065,12 +19023,12 @@
         <v>4</v>
       </c>
       <c r="I642" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>1061</v>
+        <v>1011</v>
       </c>
       <c r="E643" t="s">
         <v>4</v>
@@ -19090,7 +19048,7 @@
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>1058</v>
+        <v>1008</v>
       </c>
       <c r="E644" t="s">
         <v>4</v>
@@ -19110,7 +19068,7 @@
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>1059</v>
+        <v>1009</v>
       </c>
       <c r="E645" t="s">
         <v>4</v>
@@ -19130,7 +19088,7 @@
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>1060</v>
+        <v>1010</v>
       </c>
       <c r="E646" t="s">
         <v>4</v>
@@ -19153,10 +19111,10 @@
         <v>422</v>
       </c>
       <c r="B647" t="s">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="C647" t="s">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="E647" t="s">
         <v>4</v>
@@ -19179,13 +19137,13 @@
         <v>423</v>
       </c>
       <c r="B648" t="s">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="C648" t="s">
-        <v>670</v>
+        <v>639</v>
       </c>
       <c r="D648" t="s">
-        <v>821</v>
+        <v>771</v>
       </c>
       <c r="E648" t="s">
         <v>4</v>
@@ -19205,16 +19163,16 @@
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
-        <v>855</v>
+        <v>805</v>
       </c>
       <c r="B649" t="s">
-        <v>1122</v>
+        <v>1071</v>
       </c>
       <c r="C649" t="s">
         <v>69</v>
       </c>
       <c r="D649" t="s">
-        <v>1123</v>
+        <v>1072</v>
       </c>
       <c r="E649" t="s">
         <v>4</v>
@@ -19234,7 +19192,7 @@
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
-        <v>1062</v>
+        <v>1012</v>
       </c>
       <c r="E650" t="s">
         <v>4</v>
@@ -19257,10 +19215,10 @@
         <v>424</v>
       </c>
       <c r="C651" t="s">
-        <v>823</v>
+        <v>773</v>
       </c>
       <c r="D651" t="s">
-        <v>822</v>
+        <v>772</v>
       </c>
       <c r="E651" t="s">
         <v>4</v>
@@ -19275,7 +19233,7 @@
         <v>4</v>
       </c>
       <c r="I651" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.3">
@@ -19300,7 +19258,7 @@
     </row>
     <row r="653" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
-        <v>1063</v>
+        <v>1013</v>
       </c>
       <c r="E653" t="s">
         <v>5</v>
@@ -19315,12 +19273,12 @@
         <v>5</v>
       </c>
       <c r="I653" t="s">
-        <v>891</v>
+        <v>841</v>
       </c>
     </row>
     <row r="654" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
-        <v>1064</v>
+        <v>1014</v>
       </c>
       <c r="E654" t="s">
         <v>4</v>
@@ -19340,7 +19298,7 @@
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
-        <v>1065</v>
+        <v>1015</v>
       </c>
       <c r="E655" t="s">
         <v>4</v>
@@ -19380,7 +19338,7 @@
     </row>
     <row r="657" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
-        <v>1066</v>
+        <v>1016</v>
       </c>
       <c r="E657" t="s">
         <v>4</v>
@@ -19403,7 +19361,7 @@
         <v>429</v>
       </c>
       <c r="D658" t="s">
-        <v>824</v>
+        <v>774</v>
       </c>
       <c r="E658" t="s">
         <v>4</v>
@@ -19418,15 +19376,15 @@
         <v>4</v>
       </c>
       <c r="I658" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
-        <v>1067</v>
+        <v>1017</v>
       </c>
       <c r="D659" t="s">
-        <v>1179</v>
+        <v>1128</v>
       </c>
       <c r="E659" t="s">
         <v>4</v>
